--- a/research/traditional_assets/database/data/jordan/jordan_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_hospitals_healthcare_facilities.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0454</v>
+        <v>-0.0644</v>
       </c>
       <c r="G2">
-        <v>0.1095808383233533</v>
+        <v>-0.04993150684931507</v>
       </c>
       <c r="H2">
-        <v>0.1095808383233533</v>
+        <v>-0.04993150684931507</v>
       </c>
       <c r="I2">
-        <v>-0.251497005988024</v>
+        <v>-0.2821917808219178</v>
       </c>
       <c r="J2">
-        <v>-0.251497005988024</v>
+        <v>-0.2821917808219178</v>
       </c>
       <c r="K2">
-        <v>-3.57</v>
+        <v>-4.38</v>
       </c>
       <c r="L2">
-        <v>-0.2137724550898203</v>
+        <v>-0.3</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.595</v>
+        <v>0.4</v>
       </c>
       <c r="V2">
-        <v>0.02644444444444444</v>
+        <v>0.01544401544401545</v>
       </c>
       <c r="W2">
-        <v>-0.10625</v>
+        <v>-0.1489795918367347</v>
       </c>
       <c r="X2">
-        <v>0.1323414053601933</v>
+        <v>0.1255827894157011</v>
       </c>
       <c r="Y2">
-        <v>-0.2385914053601933</v>
+        <v>-0.2745623812524358</v>
       </c>
       <c r="Z2">
-        <v>0.4667803337339631</v>
+        <v>0.4269630062874689</v>
       </c>
       <c r="AA2">
-        <v>-0.1173938563881824</v>
+        <v>-0.1204854510893405</v>
       </c>
       <c r="AB2">
-        <v>0.1243716194505525</v>
+        <v>0.1117216975988026</v>
       </c>
       <c r="AC2">
-        <v>-0.2417654758387349</v>
+        <v>-0.2322071486881432</v>
       </c>
       <c r="AD2">
-        <v>5.39</v>
+        <v>12.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.39</v>
+        <v>12.1</v>
       </c>
       <c r="AG2">
-        <v>4.795</v>
+        <v>11.7</v>
       </c>
       <c r="AH2">
-        <v>0.1932592326998924</v>
+        <v>0.3184210526315789</v>
       </c>
       <c r="AI2">
-        <v>0.1549295774647887</v>
+        <v>0.3437499999999999</v>
       </c>
       <c r="AJ2">
-        <v>0.1756732002198205</v>
+        <v>0.3111702127659575</v>
       </c>
       <c r="AK2">
-        <v>0.1402251791197544</v>
+        <v>0.3362068965517241</v>
       </c>
       <c r="AL2">
-        <v>0.213</v>
+        <v>0.786</v>
       </c>
       <c r="AM2">
-        <v>0.058</v>
+        <v>0.593</v>
       </c>
       <c r="AN2">
-        <v>-3.934306569343065</v>
+        <v>-8.461538461538462</v>
       </c>
       <c r="AO2">
-        <v>-19.71830985915493</v>
+        <v>-5.241730279898219</v>
       </c>
       <c r="AP2">
-        <v>-3.5</v>
+        <v>-8.181818181818182</v>
       </c>
       <c r="AQ2">
-        <v>-72.41379310344828</v>
+        <v>-6.947723440134908</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0454</v>
+        <v>-0.0644</v>
       </c>
       <c r="G3">
-        <v>0.1095808383233533</v>
+        <v>-0.04993150684931507</v>
       </c>
       <c r="H3">
-        <v>0.1095808383233533</v>
+        <v>-0.04993150684931507</v>
       </c>
       <c r="I3">
-        <v>-0.251497005988024</v>
+        <v>-0.2821917808219178</v>
       </c>
       <c r="J3">
-        <v>-0.251497005988024</v>
+        <v>-0.2821917808219178</v>
       </c>
       <c r="K3">
-        <v>-3.57</v>
+        <v>-4.38</v>
       </c>
       <c r="L3">
-        <v>-0.2137724550898203</v>
+        <v>-0.3</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.595</v>
+        <v>0.4</v>
       </c>
       <c r="V3">
-        <v>0.02644444444444444</v>
+        <v>0.01544401544401545</v>
       </c>
       <c r="W3">
-        <v>-0.10625</v>
+        <v>-0.1489795918367347</v>
       </c>
       <c r="X3">
-        <v>0.1323414053601933</v>
+        <v>0.1255827894157011</v>
       </c>
       <c r="Y3">
-        <v>-0.2385914053601933</v>
+        <v>-0.2745623812524358</v>
       </c>
       <c r="Z3">
-        <v>0.4667803337339631</v>
+        <v>0.4269630062874689</v>
       </c>
       <c r="AA3">
-        <v>-0.1173938563881824</v>
+        <v>-0.1204854510893405</v>
       </c>
       <c r="AB3">
-        <v>0.1243716194505525</v>
+        <v>0.1117216975988026</v>
       </c>
       <c r="AC3">
-        <v>-0.2417654758387349</v>
+        <v>-0.2322071486881432</v>
       </c>
       <c r="AD3">
-        <v>5.39</v>
+        <v>12.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.39</v>
+        <v>12.1</v>
       </c>
       <c r="AG3">
-        <v>4.795</v>
+        <v>11.7</v>
       </c>
       <c r="AH3">
-        <v>0.1932592326998924</v>
+        <v>0.3184210526315789</v>
       </c>
       <c r="AI3">
-        <v>0.1549295774647887</v>
+        <v>0.3437499999999999</v>
       </c>
       <c r="AJ3">
-        <v>0.1756732002198205</v>
+        <v>0.3111702127659575</v>
       </c>
       <c r="AK3">
-        <v>0.1402251791197544</v>
+        <v>0.3362068965517241</v>
       </c>
       <c r="AL3">
-        <v>0.213</v>
+        <v>0.786</v>
       </c>
       <c r="AM3">
-        <v>0.058</v>
+        <v>0.593</v>
       </c>
       <c r="AN3">
-        <v>-3.934306569343065</v>
+        <v>-8.461538461538462</v>
       </c>
       <c r="AO3">
-        <v>-19.71830985915493</v>
+        <v>-5.241730279898219</v>
       </c>
       <c r="AP3">
-        <v>-3.5</v>
+        <v>-8.181818181818182</v>
       </c>
       <c r="AQ3">
-        <v>-72.41379310344828</v>
+        <v>-6.947723440134908</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jordan/jordan_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_hospitals_healthcare_facilities.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09738463569861085</v>
+        <v>0.09722586642721363</v>
       </c>
       <c r="C2">
-        <v>79.36272892768189</v>
+        <v>78.88248923073785</v>
       </c>
       <c r="D2">
-        <v>78.95472892768188</v>
+        <v>79.19848923073785</v>
       </c>
       <c r="E2">
-        <v>-19.4</v>
+        <v>-18.676</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7240000000000001</v>
       </c>
       <c r="G2">
         <v>0.408</v>
@@ -1573,28 +1573,28 @@
         <v>3.97</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0364172</v>
       </c>
       <c r="N2">
-        <v>3.97</v>
+        <v>3.9335828</v>
       </c>
       <c r="O2">
-        <v>0.794</v>
+        <v>0.78671656</v>
       </c>
       <c r="P2">
-        <v>3.176</v>
+        <v>3.14686624</v>
       </c>
       <c r="Q2">
-        <v>4.856</v>
+        <v>4.826866239999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09738463569861085</v>
+        <v>0.09780148123960973</v>
       </c>
       <c r="T2">
-        <v>0.5648729042001043</v>
+        <v>0.5694375337289941</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>109.0144217567523</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09722586642721363</v>
+        <v>0.09706709715581639</v>
       </c>
       <c r="C3">
-        <v>78.88248923073785</v>
+        <v>78.40375933824384</v>
       </c>
       <c r="D3">
-        <v>79.19848923073785</v>
+        <v>79.44375933824384</v>
       </c>
       <c r="E3">
-        <v>-18.676</v>
+        <v>-17.952</v>
       </c>
       <c r="F3">
-        <v>0.7240000000000001</v>
+        <v>1.448</v>
       </c>
       <c r="G3">
         <v>0.408</v>
@@ -1655,28 +1655,28 @@
         <v>3.97</v>
       </c>
       <c r="M3">
-        <v>0.0364172</v>
+        <v>0.07283440000000001</v>
       </c>
       <c r="N3">
-        <v>3.9335828</v>
+        <v>3.8971656</v>
       </c>
       <c r="O3">
-        <v>0.78671656</v>
+        <v>0.77943312</v>
       </c>
       <c r="P3">
-        <v>3.14686624</v>
+        <v>3.11773248</v>
       </c>
       <c r="Q3">
-        <v>4.826866239999999</v>
+        <v>4.79773248</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09780148123960973</v>
+        <v>0.09822683383246572</v>
       </c>
       <c r="T3">
-        <v>0.5694375337289941</v>
+        <v>0.5740953189625549</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>109.0144217567523</v>
+        <v>54.50721087837614</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09706709715581639</v>
+        <v>0.09690832788441918</v>
       </c>
       <c r="C4">
-        <v>78.40375933824384</v>
+        <v>77.92655332093318</v>
       </c>
       <c r="D4">
-        <v>79.44375933824384</v>
+        <v>79.69055332093318</v>
       </c>
       <c r="E4">
-        <v>-17.952</v>
+        <v>-17.228</v>
       </c>
       <c r="F4">
-        <v>1.448</v>
+        <v>2.172</v>
       </c>
       <c r="G4">
         <v>0.408</v>
@@ -1737,28 +1737,28 @@
         <v>3.97</v>
       </c>
       <c r="M4">
-        <v>0.07283440000000001</v>
+        <v>0.1092516</v>
       </c>
       <c r="N4">
-        <v>3.8971656</v>
+        <v>3.8607484</v>
       </c>
       <c r="O4">
-        <v>0.77943312</v>
+        <v>0.7721496800000001</v>
       </c>
       <c r="P4">
-        <v>3.11773248</v>
+        <v>3.08859872</v>
       </c>
       <c r="Q4">
-        <v>4.79773248</v>
+        <v>4.76859872</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09822683383246572</v>
+        <v>0.09866095658187544</v>
       </c>
       <c r="T4">
-        <v>0.5740953189625549</v>
+        <v>0.5788491410050552</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>54.50721087837614</v>
+        <v>36.3381405855841</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09690832788441918</v>
+        <v>0.09674955861302197</v>
       </c>
       <c r="C5">
-        <v>77.92655332093318</v>
+        <v>77.4508854249285</v>
       </c>
       <c r="D5">
-        <v>79.69055332093318</v>
+        <v>79.9388854249285</v>
       </c>
       <c r="E5">
-        <v>-17.228</v>
+        <v>-16.504</v>
       </c>
       <c r="F5">
-        <v>2.172</v>
+        <v>2.896</v>
       </c>
       <c r="G5">
         <v>0.408</v>
@@ -1819,28 +1819,28 @@
         <v>3.97</v>
       </c>
       <c r="M5">
-        <v>0.1092516</v>
+        <v>0.1456688</v>
       </c>
       <c r="N5">
-        <v>3.8607484</v>
+        <v>3.8243312</v>
       </c>
       <c r="O5">
-        <v>0.7721496800000001</v>
+        <v>0.7648662399999999</v>
       </c>
       <c r="P5">
-        <v>3.08859872</v>
+        <v>3.05946496</v>
       </c>
       <c r="Q5">
-        <v>4.76859872</v>
+        <v>4.739464959999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09866095658187544</v>
+        <v>0.09910412355523121</v>
       </c>
       <c r="T5">
-        <v>0.5788491410050552</v>
+        <v>0.5837020010067745</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.3381405855841</v>
+        <v>27.25360543918807</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09674955861302197</v>
+        <v>0.09659078934162472</v>
       </c>
       <c r="C6">
-        <v>77.4508854249285</v>
+        <v>76.9767700744829</v>
       </c>
       <c r="D6">
-        <v>79.9388854249285</v>
+        <v>80.1887700744829</v>
       </c>
       <c r="E6">
-        <v>-16.504</v>
+        <v>-15.78</v>
       </c>
       <c r="F6">
-        <v>2.896</v>
+        <v>3.620000000000001</v>
       </c>
       <c r="G6">
         <v>0.408</v>
@@ -1901,28 +1901,28 @@
         <v>3.97</v>
       </c>
       <c r="M6">
-        <v>0.1456688</v>
+        <v>0.182086</v>
       </c>
       <c r="N6">
-        <v>3.8243312</v>
+        <v>3.787914</v>
       </c>
       <c r="O6">
-        <v>0.7648662399999999</v>
+        <v>0.7575828</v>
       </c>
       <c r="P6">
-        <v>3.05946496</v>
+        <v>3.0303312</v>
       </c>
       <c r="Q6">
-        <v>4.739464959999999</v>
+        <v>4.7103312</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09910412355523121</v>
+        <v>0.09955662035960498</v>
       </c>
       <c r="T6">
-        <v>0.5837020010067745</v>
+        <v>0.5886570264822139</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.25360543918807</v>
+        <v>21.80288435135046</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09659078934162472</v>
+        <v>0.09643202007022751</v>
       </c>
       <c r="C7">
-        <v>76.9767700744829</v>
+        <v>76.50422187477264</v>
       </c>
       <c r="D7">
-        <v>80.1887700744829</v>
+        <v>80.44022187477263</v>
       </c>
       <c r="E7">
-        <v>-15.78</v>
+        <v>-15.056</v>
       </c>
       <c r="F7">
-        <v>3.620000000000001</v>
+        <v>4.344</v>
       </c>
       <c r="G7">
         <v>0.408</v>
@@ -1983,28 +1983,28 @@
         <v>3.97</v>
       </c>
       <c r="M7">
-        <v>0.182086</v>
+        <v>0.2185032</v>
       </c>
       <c r="N7">
-        <v>3.787914</v>
+        <v>3.7514968</v>
       </c>
       <c r="O7">
-        <v>0.7575828</v>
+        <v>0.7502993600000001</v>
       </c>
       <c r="P7">
-        <v>3.0303312</v>
+        <v>3.00119744</v>
       </c>
       <c r="Q7">
-        <v>4.7103312</v>
+        <v>4.68119744</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09955662035960498</v>
+        <v>0.1000187447555612</v>
       </c>
       <c r="T7">
-        <v>0.5886570264822139</v>
+        <v>0.593717478031599</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.80288435135046</v>
+        <v>18.16907029279205</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09643202007022751</v>
+        <v>0.09627325079883031</v>
       </c>
       <c r="C8">
-        <v>76.50422187477264</v>
+        <v>76.03325561474293</v>
       </c>
       <c r="D8">
-        <v>80.44022187477263</v>
+        <v>80.69325561474292</v>
       </c>
       <c r="E8">
-        <v>-15.056</v>
+        <v>-14.332</v>
       </c>
       <c r="F8">
-        <v>4.344</v>
+        <v>5.068</v>
       </c>
       <c r="G8">
         <v>0.408</v>
@@ -2065,28 +2065,28 @@
         <v>3.97</v>
       </c>
       <c r="M8">
-        <v>0.2185032</v>
+        <v>0.2549204</v>
       </c>
       <c r="N8">
-        <v>3.7514968</v>
+        <v>3.7150796</v>
       </c>
       <c r="O8">
-        <v>0.7502993600000001</v>
+        <v>0.7430159199999999</v>
       </c>
       <c r="P8">
-        <v>3.00119744</v>
+        <v>2.97206368</v>
       </c>
       <c r="Q8">
-        <v>4.68119744</v>
+        <v>4.652063679999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1000187447555612</v>
+        <v>0.1004908073105702</v>
       </c>
       <c r="T8">
-        <v>0.593717478031599</v>
+        <v>0.5988867564960246</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.16907029279205</v>
+        <v>15.57348882239319</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0962732507988303</v>
+        <v>0.09611448152743308</v>
       </c>
       <c r="C9">
-        <v>76.03325561474296</v>
+        <v>75.5638862700074</v>
       </c>
       <c r="D9">
-        <v>80.69325561474295</v>
+        <v>80.9478862700074</v>
       </c>
       <c r="E9">
-        <v>-14.332</v>
+        <v>-13.608</v>
       </c>
       <c r="F9">
-        <v>5.068000000000001</v>
+        <v>5.792000000000001</v>
       </c>
       <c r="G9">
         <v>0.408</v>
@@ -2147,28 +2147,28 @@
         <v>3.97</v>
       </c>
       <c r="M9">
-        <v>0.2549204</v>
+        <v>0.2913376</v>
       </c>
       <c r="N9">
-        <v>3.7150796</v>
+        <v>3.6786624</v>
       </c>
       <c r="O9">
-        <v>0.7430159199999999</v>
+        <v>0.73573248</v>
       </c>
       <c r="P9">
-        <v>2.97206368</v>
+        <v>2.94292992</v>
       </c>
       <c r="Q9">
-        <v>4.652063679999999</v>
+        <v>4.62292992</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1004908073105702</v>
+        <v>0.1009731320950359</v>
       </c>
       <c r="T9">
-        <v>0.5988867564960246</v>
+        <v>0.604168410579242</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.57348882239319</v>
+        <v>13.62680271959404</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09611448152743308</v>
+        <v>0.09606371225603585</v>
       </c>
       <c r="C10">
-        <v>75.5638862700074</v>
+        <v>74.92164834094518</v>
       </c>
       <c r="D10">
-        <v>80.9478862700074</v>
+        <v>81.02964834094519</v>
       </c>
       <c r="E10">
-        <v>-13.608</v>
+        <v>-12.884</v>
       </c>
       <c r="F10">
-        <v>5.792000000000001</v>
+        <v>6.516</v>
       </c>
       <c r="G10">
         <v>0.408</v>
@@ -2229,45 +2229,45 @@
         <v>3.97</v>
       </c>
       <c r="M10">
-        <v>0.2913376</v>
+        <v>0.3375288</v>
       </c>
       <c r="N10">
-        <v>3.6786624</v>
+        <v>3.6324712</v>
       </c>
       <c r="O10">
-        <v>0.73573248</v>
+        <v>0.7264942400000001</v>
       </c>
       <c r="P10">
-        <v>2.94292992</v>
+        <v>2.90597696</v>
       </c>
       <c r="Q10">
-        <v>4.62292992</v>
+        <v>4.58597696</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1009731320950359</v>
+        <v>0.1014660574242152</v>
       </c>
       <c r="T10">
-        <v>0.604168410579242</v>
+        <v>0.6095661449719806</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.62680271959404</v>
+        <v>11.76195927577143</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09606371225603585</v>
+        <v>0.09591694298463863</v>
       </c>
       <c r="C11">
-        <v>74.92164834094518</v>
+        <v>74.43494658262405</v>
       </c>
       <c r="D11">
-        <v>81.02964834094519</v>
+        <v>81.26694658262404</v>
       </c>
       <c r="E11">
-        <v>-12.884</v>
+        <v>-12.16</v>
       </c>
       <c r="F11">
-        <v>6.516</v>
+        <v>7.24</v>
       </c>
       <c r="G11">
         <v>0.408</v>
@@ -2311,28 +2311,28 @@
         <v>3.97</v>
       </c>
       <c r="M11">
-        <v>0.3375288</v>
+        <v>0.375032</v>
       </c>
       <c r="N11">
-        <v>3.6324712</v>
+        <v>3.594968</v>
       </c>
       <c r="O11">
-        <v>0.7264942400000001</v>
+        <v>0.7189936</v>
       </c>
       <c r="P11">
-        <v>2.90597696</v>
+        <v>2.8759744</v>
       </c>
       <c r="Q11">
-        <v>4.58597696</v>
+        <v>4.555974399999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1014660574242152</v>
+        <v>0.1019699366495985</v>
       </c>
       <c r="T11">
-        <v>0.6095661449719806</v>
+        <v>0.6150838290178913</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.76195927577143</v>
+        <v>10.58576334819429</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09591694298463864</v>
+        <v>0.09591977371324141</v>
       </c>
       <c r="C12">
-        <v>74.43494658262404</v>
+        <v>73.70635668420455</v>
       </c>
       <c r="D12">
-        <v>81.26694658262403</v>
+        <v>81.26235668420455</v>
       </c>
       <c r="E12">
-        <v>-12.16</v>
+        <v>-11.436</v>
       </c>
       <c r="F12">
-        <v>7.240000000000001</v>
+        <v>7.964</v>
       </c>
       <c r="G12">
         <v>0.408</v>
@@ -2393,45 +2393,45 @@
         <v>3.97</v>
       </c>
       <c r="M12">
-        <v>0.375032</v>
+        <v>0.426074</v>
       </c>
       <c r="N12">
-        <v>3.594968</v>
+        <v>3.543926</v>
       </c>
       <c r="O12">
-        <v>0.7189936</v>
+        <v>0.7087852</v>
       </c>
       <c r="P12">
-        <v>2.8759744</v>
+        <v>2.8351408</v>
       </c>
       <c r="Q12">
-        <v>4.555974399999999</v>
+        <v>4.515140799999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1019699366495985</v>
+        <v>0.102485139003642</v>
       </c>
       <c r="T12">
-        <v>0.6150838290178914</v>
+        <v>0.62072550596371</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.58576334819429</v>
+        <v>9.317630270798031</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09591977371324141</v>
+        <v>0.09578660444184418</v>
       </c>
       <c r="C13">
-        <v>73.70635668420455</v>
+        <v>73.19884766118712</v>
       </c>
       <c r="D13">
-        <v>81.26235668420455</v>
+        <v>81.47884766118712</v>
       </c>
       <c r="E13">
-        <v>-11.436</v>
+        <v>-10.712</v>
       </c>
       <c r="F13">
-        <v>7.964</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="G13">
         <v>0.408</v>
@@ -2475,28 +2475,28 @@
         <v>3.97</v>
       </c>
       <c r="M13">
-        <v>0.426074</v>
+        <v>0.464808</v>
       </c>
       <c r="N13">
-        <v>3.543926</v>
+        <v>3.505192</v>
       </c>
       <c r="O13">
-        <v>0.7087852</v>
+        <v>0.7010384</v>
       </c>
       <c r="P13">
-        <v>2.8351408</v>
+        <v>2.8041536</v>
       </c>
       <c r="Q13">
-        <v>4.515140799999999</v>
+        <v>4.484153599999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.102485139003642</v>
+        <v>0.1030120505020957</v>
       </c>
       <c r="T13">
-        <v>0.62072550596371</v>
+        <v>0.6264954028401156</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.317630270798031</v>
+        <v>8.54116108156486</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09578660444184418</v>
+        <v>0.09565343517044697</v>
       </c>
       <c r="C14">
-        <v>73.19884766118712</v>
+        <v>72.69249522629929</v>
       </c>
       <c r="D14">
-        <v>81.47884766118712</v>
+        <v>81.69649522629929</v>
       </c>
       <c r="E14">
-        <v>-10.712</v>
+        <v>-9.987999999999998</v>
       </c>
       <c r="F14">
-        <v>8.688000000000001</v>
+        <v>9.412000000000001</v>
       </c>
       <c r="G14">
         <v>0.408</v>
@@ -2557,28 +2557,28 @@
         <v>3.97</v>
       </c>
       <c r="M14">
-        <v>0.464808</v>
+        <v>0.503542</v>
       </c>
       <c r="N14">
-        <v>3.505192</v>
+        <v>3.466458</v>
       </c>
       <c r="O14">
-        <v>0.7010384</v>
+        <v>0.6932916</v>
       </c>
       <c r="P14">
-        <v>2.8041536</v>
+        <v>2.7731664</v>
       </c>
       <c r="Q14">
-        <v>4.484153599999999</v>
+        <v>4.4531664</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1030120505020957</v>
+        <v>0.1035510749085597</v>
       </c>
       <c r="T14">
-        <v>0.6264954028401156</v>
+        <v>0.6323979410240248</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.54116108156486</v>
+        <v>7.884148690675255</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09565343517044697</v>
+        <v>0.09560986589904975</v>
       </c>
       <c r="C15">
-        <v>72.69249522629929</v>
+        <v>72.03995610475117</v>
       </c>
       <c r="D15">
-        <v>81.69649522629929</v>
+        <v>81.76795610475116</v>
       </c>
       <c r="E15">
-        <v>-9.987999999999998</v>
+        <v>-9.263999999999998</v>
       </c>
       <c r="F15">
-        <v>9.412000000000001</v>
+        <v>10.136</v>
       </c>
       <c r="G15">
         <v>0.408</v>
@@ -2639,45 +2639,45 @@
         <v>3.97</v>
       </c>
       <c r="M15">
-        <v>0.503542</v>
+        <v>0.5503848000000001</v>
       </c>
       <c r="N15">
-        <v>3.466458</v>
+        <v>3.4196152</v>
       </c>
       <c r="O15">
-        <v>0.6932916</v>
+        <v>0.6839230399999999</v>
       </c>
       <c r="P15">
-        <v>2.7731664</v>
+        <v>2.73569216</v>
       </c>
       <c r="Q15">
-        <v>4.4531664</v>
+        <v>4.415692159999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1035510749085597</v>
+        <v>0.1041026347663369</v>
       </c>
       <c r="T15">
-        <v>0.6323979410240248</v>
+        <v>0.6384377475377923</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.884148690675255</v>
+        <v>7.21313524646756</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09560986589904975</v>
+        <v>0.09548309662765252</v>
       </c>
       <c r="C16">
-        <v>72.03995610475117</v>
+        <v>71.52459173583361</v>
       </c>
       <c r="D16">
-        <v>81.76795610475116</v>
+        <v>81.97659173583361</v>
       </c>
       <c r="E16">
-        <v>-9.263999999999998</v>
+        <v>-8.539999999999996</v>
       </c>
       <c r="F16">
-        <v>10.136</v>
+        <v>10.86</v>
       </c>
       <c r="G16">
         <v>0.408</v>
@@ -2721,28 +2721,28 @@
         <v>3.97</v>
       </c>
       <c r="M16">
-        <v>0.5503848000000001</v>
+        <v>0.5896980000000002</v>
       </c>
       <c r="N16">
-        <v>3.4196152</v>
+        <v>3.380301999999999</v>
       </c>
       <c r="O16">
-        <v>0.6839230399999999</v>
+        <v>0.6760603999999999</v>
       </c>
       <c r="P16">
-        <v>2.73569216</v>
+        <v>2.7042416</v>
       </c>
       <c r="Q16">
-        <v>4.415692159999999</v>
+        <v>4.384241599999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1041026347663369</v>
+        <v>0.1046671725031206</v>
       </c>
       <c r="T16">
-        <v>0.6384377475377923</v>
+        <v>0.6446196671460013</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.21313524646756</v>
+        <v>6.732259563369722</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0954830966276525</v>
+        <v>0.09535632735625529</v>
       </c>
       <c r="C17">
-        <v>71.52459173583364</v>
+        <v>71.01029478205153</v>
       </c>
       <c r="D17">
-        <v>81.97659173583364</v>
+        <v>82.18629478205153</v>
       </c>
       <c r="E17">
-        <v>-8.539999999999997</v>
+        <v>-7.815999999999997</v>
       </c>
       <c r="F17">
-        <v>10.86</v>
+        <v>11.584</v>
       </c>
       <c r="G17">
         <v>0.408</v>
@@ -2803,28 +2803,28 @@
         <v>3.97</v>
       </c>
       <c r="M17">
-        <v>0.5896980000000001</v>
+        <v>0.6290112000000001</v>
       </c>
       <c r="N17">
-        <v>3.380301999999999</v>
+        <v>3.3409888</v>
       </c>
       <c r="O17">
-        <v>0.6760603999999999</v>
+        <v>0.66819776</v>
       </c>
       <c r="P17">
-        <v>2.7042416</v>
+        <v>2.67279104</v>
       </c>
       <c r="Q17">
-        <v>4.384241599999999</v>
+        <v>4.35279104</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1046671725031206</v>
+        <v>0.1052451516145896</v>
       </c>
       <c r="T17">
-        <v>0.6446196671460013</v>
+        <v>0.6509487753163106</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.732259563369723</v>
+        <v>6.311493340659116</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09535632735625529</v>
+        <v>0.09536555808485808</v>
       </c>
       <c r="C18">
-        <v>71.01029478205153</v>
+        <v>70.27098900498949</v>
       </c>
       <c r="D18">
-        <v>82.18629478205153</v>
+        <v>82.17098900498949</v>
       </c>
       <c r="E18">
-        <v>-7.815999999999997</v>
+        <v>-7.091999999999997</v>
       </c>
       <c r="F18">
-        <v>11.584</v>
+        <v>12.308</v>
       </c>
       <c r="G18">
         <v>0.408</v>
@@ -2885,45 +2885,45 @@
         <v>3.97</v>
       </c>
       <c r="M18">
-        <v>0.6290112000000001</v>
+        <v>0.6806324000000001</v>
       </c>
       <c r="N18">
-        <v>3.3409888</v>
+        <v>3.289367599999999</v>
       </c>
       <c r="O18">
-        <v>0.66819776</v>
+        <v>0.6578735199999999</v>
       </c>
       <c r="P18">
-        <v>2.67279104</v>
+        <v>2.63149408</v>
       </c>
       <c r="Q18">
-        <v>4.35279104</v>
+        <v>4.311494079999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1052451516145896</v>
+        <v>0.1058370579335639</v>
       </c>
       <c r="T18">
-        <v>0.6509487753163106</v>
+        <v>0.6574303921172298</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.311493340659116</v>
+        <v>5.832810780092159</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09536555808485808</v>
+        <v>0.09524678881346087</v>
       </c>
       <c r="C19">
-        <v>70.27098900498949</v>
+        <v>69.74436053766736</v>
       </c>
       <c r="D19">
-        <v>82.17098900498949</v>
+        <v>82.36836053766736</v>
       </c>
       <c r="E19">
-        <v>-7.091999999999997</v>
+        <v>-6.367999999999997</v>
       </c>
       <c r="F19">
-        <v>12.308</v>
+        <v>13.032</v>
       </c>
       <c r="G19">
         <v>0.408</v>
@@ -2967,28 +2967,28 @@
         <v>3.97</v>
       </c>
       <c r="M19">
-        <v>0.6806324000000001</v>
+        <v>0.7206696000000001</v>
       </c>
       <c r="N19">
-        <v>3.289367599999999</v>
+        <v>3.2493304</v>
       </c>
       <c r="O19">
-        <v>0.6578735199999999</v>
+        <v>0.64986608</v>
       </c>
       <c r="P19">
-        <v>2.63149408</v>
+        <v>2.59946432</v>
       </c>
       <c r="Q19">
-        <v>4.311494079999999</v>
+        <v>4.27946432</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1058370579335639</v>
+        <v>0.1064434009920255</v>
       </c>
       <c r="T19">
-        <v>0.6574303921172298</v>
+        <v>0.6640700971328056</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.832810780092159</v>
+        <v>5.508765736753707</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09524678881346087</v>
+        <v>0.09512801954206364</v>
       </c>
       <c r="C20">
-        <v>69.74436053766736</v>
+        <v>69.21868251081898</v>
       </c>
       <c r="D20">
-        <v>82.36836053766736</v>
+        <v>82.56668251081898</v>
       </c>
       <c r="E20">
-        <v>-6.367999999999999</v>
+        <v>-5.643999999999997</v>
       </c>
       <c r="F20">
-        <v>13.032</v>
+        <v>13.756</v>
       </c>
       <c r="G20">
         <v>0.408</v>
@@ -3049,28 +3049,28 @@
         <v>3.97</v>
       </c>
       <c r="M20">
-        <v>0.7206696</v>
+        <v>0.7607068000000001</v>
       </c>
       <c r="N20">
-        <v>3.2493304</v>
+        <v>3.209293199999999</v>
       </c>
       <c r="O20">
-        <v>0.64986608</v>
+        <v>0.6418586399999999</v>
       </c>
       <c r="P20">
-        <v>2.59946432</v>
+        <v>2.56743456</v>
       </c>
       <c r="Q20">
-        <v>4.27946432</v>
+        <v>4.247434559999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1064434009920254</v>
+        <v>0.1070647154840292</v>
       </c>
       <c r="T20">
-        <v>0.6640700971328055</v>
+        <v>0.6708737454820992</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.508765736753707</v>
+        <v>5.218830697977196</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09512801954206364</v>
+        <v>0.09500925027066641</v>
       </c>
       <c r="C21">
-        <v>69.21868251081898</v>
+        <v>68.69396180626764</v>
       </c>
       <c r="D21">
-        <v>82.56668251081898</v>
+        <v>82.76596180626764</v>
       </c>
       <c r="E21">
-        <v>-5.643999999999997</v>
+        <v>-4.919999999999996</v>
       </c>
       <c r="F21">
-        <v>13.756</v>
+        <v>14.48</v>
       </c>
       <c r="G21">
         <v>0.408</v>
@@ -3131,28 +3131,28 @@
         <v>3.97</v>
       </c>
       <c r="M21">
-        <v>0.7607068000000001</v>
+        <v>0.8007440000000001</v>
       </c>
       <c r="N21">
-        <v>3.209293199999999</v>
+        <v>3.169256</v>
       </c>
       <c r="O21">
-        <v>0.6418586399999999</v>
+        <v>0.6338512000000001</v>
       </c>
       <c r="P21">
-        <v>2.56743456</v>
+        <v>2.5354048</v>
       </c>
       <c r="Q21">
-        <v>4.247434559999999</v>
+        <v>4.2154048</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1070647154840292</v>
+        <v>0.107701562838333</v>
       </c>
       <c r="T21">
-        <v>0.6708737454820992</v>
+        <v>0.6778474850401252</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.218830697977196</v>
+        <v>4.957889163078336</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09500925027066641</v>
+        <v>0.09489048099926921</v>
       </c>
       <c r="C22">
-        <v>68.69396180626764</v>
+        <v>68.17020537243611</v>
       </c>
       <c r="D22">
-        <v>82.76596180626764</v>
+        <v>82.96620537243612</v>
       </c>
       <c r="E22">
-        <v>-4.919999999999996</v>
+        <v>-4.195999999999996</v>
       </c>
       <c r="F22">
-        <v>14.48</v>
+        <v>15.204</v>
       </c>
       <c r="G22">
         <v>0.408</v>
@@ -3213,28 +3213,28 @@
         <v>3.97</v>
       </c>
       <c r="M22">
-        <v>0.8007440000000001</v>
+        <v>0.8407812000000001</v>
       </c>
       <c r="N22">
-        <v>3.169256</v>
+        <v>3.129218799999999</v>
       </c>
       <c r="O22">
-        <v>0.6338512000000001</v>
+        <v>0.62584376</v>
       </c>
       <c r="P22">
-        <v>2.5354048</v>
+        <v>2.503375039999999</v>
       </c>
       <c r="Q22">
-        <v>4.2154048</v>
+        <v>4.18337504</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.107701562838333</v>
+        <v>0.1083545329104673</v>
       </c>
       <c r="T22">
-        <v>0.6778474850401252</v>
+        <v>0.6849977749667088</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.957889163078336</v>
+        <v>4.721799202931749</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09489048099926921</v>
+        <v>0.09477171172787197</v>
       </c>
       <c r="C23">
-        <v>68.17020537243613</v>
+        <v>67.64742022515425</v>
       </c>
       <c r="D23">
-        <v>82.96620537243612</v>
+        <v>83.16742022515425</v>
       </c>
       <c r="E23">
-        <v>-4.195999999999998</v>
+        <v>-3.471999999999998</v>
       </c>
       <c r="F23">
-        <v>15.204</v>
+        <v>15.928</v>
       </c>
       <c r="G23">
         <v>0.408</v>
@@ -3295,28 +3295,28 @@
         <v>3.97</v>
       </c>
       <c r="M23">
-        <v>0.8407812000000001</v>
+        <v>0.8808184000000001</v>
       </c>
       <c r="N23">
-        <v>3.129218799999999</v>
+        <v>3.0891816</v>
       </c>
       <c r="O23">
-        <v>0.62584376</v>
+        <v>0.61783632</v>
       </c>
       <c r="P23">
-        <v>2.503375039999999</v>
+        <v>2.47134528</v>
       </c>
       <c r="Q23">
-        <v>4.18337504</v>
+        <v>4.151345279999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1083545329104673</v>
+        <v>0.1090242458049641</v>
       </c>
       <c r="T23">
-        <v>0.6849977749667088</v>
+        <v>0.6923314056606407</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.721799202931749</v>
+        <v>4.507171966434852</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09477171172787197</v>
+        <v>0.09511294245647477</v>
       </c>
       <c r="C24">
-        <v>67.64742022515425</v>
+        <v>66.34792669372497</v>
       </c>
       <c r="D24">
-        <v>83.16742022515425</v>
+        <v>82.59192669372497</v>
       </c>
       <c r="E24">
-        <v>-3.471999999999998</v>
+        <v>-2.747999999999998</v>
       </c>
       <c r="F24">
-        <v>15.928</v>
+        <v>16.652</v>
       </c>
       <c r="G24">
         <v>0.408</v>
@@ -3377,45 +3377,45 @@
         <v>3.97</v>
       </c>
       <c r="M24">
-        <v>0.8808184000000001</v>
+        <v>0.9624856000000002</v>
       </c>
       <c r="N24">
-        <v>3.0891816</v>
+        <v>3.0075144</v>
       </c>
       <c r="O24">
-        <v>0.61783632</v>
+        <v>0.60150288</v>
       </c>
       <c r="P24">
-        <v>2.47134528</v>
+        <v>2.40601152</v>
       </c>
       <c r="Q24">
-        <v>4.151345279999999</v>
+        <v>4.08601152</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1090242458049641</v>
+        <v>0.1097113538395776</v>
       </c>
       <c r="T24">
-        <v>0.6923314056606407</v>
+        <v>0.6998555202687007</v>
       </c>
       <c r="U24">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.507171966434852</v>
+        <v>4.12473703502681</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09511294245647477</v>
+        <v>0.09568617318507754</v>
       </c>
       <c r="C25">
-        <v>66.34792669372497</v>
+        <v>64.67488155170328</v>
       </c>
       <c r="D25">
-        <v>82.59192669372497</v>
+        <v>81.64288155170328</v>
       </c>
       <c r="E25">
-        <v>-2.747999999999998</v>
+        <v>-2.023999999999997</v>
       </c>
       <c r="F25">
-        <v>16.652</v>
+        <v>17.376</v>
       </c>
       <c r="G25">
         <v>0.408</v>
@@ -3459,45 +3459,45 @@
         <v>3.97</v>
       </c>
       <c r="M25">
-        <v>0.9624856000000002</v>
+        <v>1.0651488</v>
       </c>
       <c r="N25">
-        <v>3.0075144</v>
+        <v>2.9048512</v>
       </c>
       <c r="O25">
-        <v>0.60150288</v>
+        <v>0.58097024</v>
       </c>
       <c r="P25">
-        <v>2.40601152</v>
+        <v>2.323880959999999</v>
       </c>
       <c r="Q25">
-        <v>4.08601152</v>
+        <v>4.003880959999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1097113538395776</v>
+        <v>0.1104165436645757</v>
       </c>
       <c r="T25">
-        <v>0.6998555202687007</v>
+        <v>0.7075776378927623</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.12473703502681</v>
+        <v>3.72717877539739</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09568617318507754</v>
+        <v>0.09561540391368031</v>
       </c>
       <c r="C26">
-        <v>64.67488155170328</v>
+        <v>64.0668659016886</v>
       </c>
       <c r="D26">
-        <v>81.64288155170328</v>
+        <v>81.75886590168859</v>
       </c>
       <c r="E26">
-        <v>-2.023999999999997</v>
+        <v>-1.299999999999997</v>
       </c>
       <c r="F26">
-        <v>17.376</v>
+        <v>18.1</v>
       </c>
       <c r="G26">
         <v>0.408</v>
@@ -3541,28 +3541,28 @@
         <v>3.97</v>
       </c>
       <c r="M26">
-        <v>1.0651488</v>
+        <v>1.10953</v>
       </c>
       <c r="N26">
-        <v>2.9048512</v>
+        <v>2.860469999999999</v>
       </c>
       <c r="O26">
-        <v>0.58097024</v>
+        <v>0.5720939999999999</v>
       </c>
       <c r="P26">
-        <v>2.323880959999999</v>
+        <v>2.288376</v>
       </c>
       <c r="Q26">
-        <v>4.003880959999999</v>
+        <v>3.968375999999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1104165436645757</v>
+        <v>0.1111405385515737</v>
       </c>
       <c r="T26">
-        <v>0.7075776378927622</v>
+        <v>0.7155056786534654</v>
       </c>
       <c r="U26">
         <v>0.0613</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.72717877539739</v>
+        <v>3.578091624381494</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09561540391368031</v>
+        <v>0.09612703464228309</v>
       </c>
       <c r="C27">
-        <v>64.0668659016886</v>
+        <v>62.51169537021697</v>
       </c>
       <c r="D27">
-        <v>81.75886590168859</v>
+        <v>80.92769537021697</v>
       </c>
       <c r="E27">
-        <v>-1.299999999999997</v>
+        <v>-0.575999999999997</v>
       </c>
       <c r="F27">
-        <v>18.1</v>
+        <v>18.824</v>
       </c>
       <c r="G27">
         <v>0.408</v>
@@ -3623,45 +3623,45 @@
         <v>3.97</v>
       </c>
       <c r="M27">
-        <v>1.10953</v>
+        <v>1.2066184</v>
       </c>
       <c r="N27">
-        <v>2.860469999999999</v>
+        <v>2.7633816</v>
       </c>
       <c r="O27">
-        <v>0.5720939999999999</v>
+        <v>0.55267632</v>
       </c>
       <c r="P27">
-        <v>2.288376</v>
+        <v>2.21070528</v>
       </c>
       <c r="Q27">
-        <v>3.968375999999999</v>
+        <v>3.89070528</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1111405385515737</v>
+        <v>0.1118841008679501</v>
       </c>
       <c r="T27">
-        <v>0.7155056786534654</v>
+        <v>0.7236479907860796</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.578091624381494</v>
+        <v>3.290186856093028</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09612703464228309</v>
+        <v>0.09607866537088586</v>
       </c>
       <c r="C28">
-        <v>62.51169537021697</v>
+        <v>61.86554973711472</v>
       </c>
       <c r="D28">
-        <v>80.92769537021697</v>
+        <v>81.00554973711472</v>
       </c>
       <c r="E28">
-        <v>-0.575999999999997</v>
+        <v>0.1480000000000032</v>
       </c>
       <c r="F28">
-        <v>18.824</v>
+        <v>19.548</v>
       </c>
       <c r="G28">
         <v>0.408</v>
@@ -3705,28 +3705,28 @@
         <v>3.97</v>
       </c>
       <c r="M28">
-        <v>1.2066184</v>
+        <v>1.2530268</v>
       </c>
       <c r="N28">
-        <v>2.7633816</v>
+        <v>2.7169732</v>
       </c>
       <c r="O28">
-        <v>0.55267632</v>
+        <v>0.5433946399999999</v>
       </c>
       <c r="P28">
-        <v>2.21070528</v>
+        <v>2.17357856</v>
       </c>
       <c r="Q28">
-        <v>3.89070528</v>
+        <v>3.853578559999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1118841008679501</v>
+        <v>0.1126480347546382</v>
       </c>
       <c r="T28">
-        <v>0.7236479907860796</v>
+        <v>0.7320133799634229</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.290186856093028</v>
+        <v>3.168328083645138</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09607866537088586</v>
+        <v>0.09603029609948865</v>
       </c>
       <c r="C29">
-        <v>61.86554973711472</v>
+        <v>61.2195540437617</v>
       </c>
       <c r="D29">
-        <v>81.00554973711472</v>
+        <v>81.08355404376171</v>
       </c>
       <c r="E29">
-        <v>0.1480000000000032</v>
+        <v>0.8720000000000034</v>
       </c>
       <c r="F29">
-        <v>19.548</v>
+        <v>20.272</v>
       </c>
       <c r="G29">
         <v>0.408</v>
@@ -3787,28 +3787,28 @@
         <v>3.97</v>
       </c>
       <c r="M29">
-        <v>1.2530268</v>
+        <v>1.2994352</v>
       </c>
       <c r="N29">
-        <v>2.7169732</v>
+        <v>2.670564799999999</v>
       </c>
       <c r="O29">
-        <v>0.5433946399999999</v>
+        <v>0.5341129599999999</v>
       </c>
       <c r="P29">
-        <v>2.17357856</v>
+        <v>2.136451839999999</v>
       </c>
       <c r="Q29">
-        <v>3.853578559999999</v>
+        <v>3.816451839999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1126480347546382</v>
+        <v>0.1134331890270676</v>
       </c>
       <c r="T29">
-        <v>0.7320133799634229</v>
+        <v>0.7406111410623589</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.168328083645138</v>
+        <v>3.05517350922924</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09603029609948865</v>
+        <v>0.09779152682809143</v>
       </c>
       <c r="C30">
-        <v>61.2195540437617</v>
+        <v>57.74882095707271</v>
       </c>
       <c r="D30">
-        <v>81.08355404376171</v>
+        <v>78.33682095707272</v>
       </c>
       <c r="E30">
-        <v>0.8720000000000034</v>
+        <v>1.596000000000007</v>
       </c>
       <c r="F30">
-        <v>20.272</v>
+        <v>20.99600000000001</v>
       </c>
       <c r="G30">
         <v>0.408</v>
@@ -3869,45 +3869,45 @@
         <v>3.97</v>
       </c>
       <c r="M30">
-        <v>1.2994352</v>
+        <v>1.509612400000001</v>
       </c>
       <c r="N30">
-        <v>2.670564799999999</v>
+        <v>2.460387599999999</v>
       </c>
       <c r="O30">
-        <v>0.5341129599999999</v>
+        <v>0.4920775199999998</v>
       </c>
       <c r="P30">
-        <v>2.136451839999999</v>
+        <v>1.968310079999999</v>
       </c>
       <c r="Q30">
-        <v>3.816451839999999</v>
+        <v>3.648310079999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1134331890270676</v>
+        <v>0.1142404603212555</v>
       </c>
       <c r="T30">
-        <v>0.7406111410623589</v>
+        <v>0.7494510926147863</v>
       </c>
       <c r="U30">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.05517350922924</v>
+        <v>2.629814116524214</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09779152682809142</v>
+        <v>0.09780555755669421</v>
       </c>
       <c r="C31">
-        <v>57.74882095707277</v>
+        <v>57.0036862413598</v>
       </c>
       <c r="D31">
-        <v>78.33682095707276</v>
+        <v>78.3156862413598</v>
       </c>
       <c r="E31">
-        <v>1.596</v>
+        <v>2.320000000000004</v>
       </c>
       <c r="F31">
-        <v>20.996</v>
+        <v>21.72</v>
       </c>
       <c r="G31">
         <v>0.408</v>
@@ -3951,28 +3951,28 @@
         <v>3.97</v>
       </c>
       <c r="M31">
-        <v>1.5096124</v>
+        <v>1.561668</v>
       </c>
       <c r="N31">
-        <v>2.4603876</v>
+        <v>2.408332</v>
       </c>
       <c r="O31">
-        <v>0.49207752</v>
+        <v>0.4816663999999999</v>
       </c>
       <c r="P31">
-        <v>1.96831008</v>
+        <v>1.9266656</v>
       </c>
       <c r="Q31">
-        <v>3.648310079999999</v>
+        <v>3.606665599999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1142404603212555</v>
+        <v>0.1150707965095631</v>
       </c>
       <c r="T31">
-        <v>0.7494510926147863</v>
+        <v>0.7585436142115687</v>
       </c>
       <c r="U31">
         <v>0.07190000000000001</v>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.629814116524215</v>
+        <v>2.542153645973408</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09780555755669421</v>
+        <v>0.09878678828529697</v>
       </c>
       <c r="C32">
-        <v>57.0036862413598</v>
+        <v>54.82940475877827</v>
       </c>
       <c r="D32">
-        <v>78.3156862413598</v>
+        <v>76.86540475877827</v>
       </c>
       <c r="E32">
-        <v>2.320000000000004</v>
+        <v>3.044000000000004</v>
       </c>
       <c r="F32">
-        <v>21.72</v>
+        <v>22.444</v>
       </c>
       <c r="G32">
         <v>0.408</v>
@@ -4033,45 +4033,45 @@
         <v>3.97</v>
       </c>
       <c r="M32">
-        <v>1.561668</v>
+        <v>1.7012552</v>
       </c>
       <c r="N32">
-        <v>2.408332</v>
+        <v>2.268744799999999</v>
       </c>
       <c r="O32">
-        <v>0.4816663999999999</v>
+        <v>0.4537489599999999</v>
       </c>
       <c r="P32">
-        <v>1.9266656</v>
+        <v>1.814995839999999</v>
       </c>
       <c r="Q32">
-        <v>3.606665599999999</v>
+        <v>3.494995839999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1150707965095631</v>
+        <v>0.1159252004134739</v>
       </c>
       <c r="T32">
-        <v>0.7585436142115687</v>
+        <v>0.7678996871589824</v>
       </c>
       <c r="U32">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.542153645973408</v>
+        <v>2.333571118548234</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09878678828529697</v>
+        <v>0.09883201901389975</v>
       </c>
       <c r="C33">
-        <v>54.82940475877827</v>
+        <v>54.03984666149601</v>
       </c>
       <c r="D33">
-        <v>76.86540475877827</v>
+        <v>76.79984666149602</v>
       </c>
       <c r="E33">
-        <v>3.044000000000004</v>
+        <v>3.768000000000004</v>
       </c>
       <c r="F33">
-        <v>22.444</v>
+        <v>23.168</v>
       </c>
       <c r="G33">
         <v>0.408</v>
@@ -4115,28 +4115,28 @@
         <v>3.97</v>
       </c>
       <c r="M33">
-        <v>1.7012552</v>
+        <v>1.7561344</v>
       </c>
       <c r="N33">
-        <v>2.268744799999999</v>
+        <v>2.213865599999999</v>
       </c>
       <c r="O33">
-        <v>0.4537489599999999</v>
+        <v>0.4427731199999999</v>
       </c>
       <c r="P33">
-        <v>1.814995839999999</v>
+        <v>1.771092479999999</v>
       </c>
       <c r="Q33">
-        <v>3.494995839999999</v>
+        <v>3.451092479999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1159252004134739</v>
+        <v>0.1168047338439702</v>
       </c>
       <c r="T33">
-        <v>0.7678996871589824</v>
+        <v>0.7775309387224965</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.333571118548234</v>
+        <v>2.260647021093601</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09883201901389975</v>
+        <v>0.09887724974250253</v>
       </c>
       <c r="C34">
-        <v>54.03984666149601</v>
+        <v>53.25040029722631</v>
       </c>
       <c r="D34">
-        <v>76.79984666149602</v>
+        <v>76.73440029722632</v>
       </c>
       <c r="E34">
-        <v>3.768000000000004</v>
+        <v>4.492000000000004</v>
       </c>
       <c r="F34">
-        <v>23.168</v>
+        <v>23.892</v>
       </c>
       <c r="G34">
         <v>0.408</v>
@@ -4197,28 +4197,28 @@
         <v>3.97</v>
       </c>
       <c r="M34">
-        <v>1.7561344</v>
+        <v>1.8110136</v>
       </c>
       <c r="N34">
-        <v>2.213865599999999</v>
+        <v>2.158986399999999</v>
       </c>
       <c r="O34">
-        <v>0.4427731199999999</v>
+        <v>0.4317972799999999</v>
       </c>
       <c r="P34">
-        <v>1.771092479999999</v>
+        <v>1.72718912</v>
       </c>
       <c r="Q34">
-        <v>3.451092479999999</v>
+        <v>3.407189119999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1168047338439702</v>
+        <v>0.1177105220037351</v>
       </c>
       <c r="T34">
-        <v>0.7775309387224965</v>
+        <v>0.7874496903326828</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.260647021093601</v>
+        <v>2.192142565908947</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09887724974250253</v>
+        <v>0.0989224804711053</v>
       </c>
       <c r="C35">
-        <v>53.25040029722631</v>
+        <v>52.46106538056655</v>
       </c>
       <c r="D35">
-        <v>76.73440029722632</v>
+        <v>76.66906538056655</v>
       </c>
       <c r="E35">
-        <v>4.492000000000004</v>
+        <v>5.216000000000005</v>
       </c>
       <c r="F35">
-        <v>23.892</v>
+        <v>24.616</v>
       </c>
       <c r="G35">
         <v>0.408</v>
@@ -4279,28 +4279,28 @@
         <v>3.97</v>
       </c>
       <c r="M35">
-        <v>1.8110136</v>
+        <v>1.8658928</v>
       </c>
       <c r="N35">
-        <v>2.158986399999999</v>
+        <v>2.1041072</v>
       </c>
       <c r="O35">
-        <v>0.4317972799999999</v>
+        <v>0.4208214399999999</v>
       </c>
       <c r="P35">
-        <v>1.72718912</v>
+        <v>1.68328576</v>
       </c>
       <c r="Q35">
-        <v>3.407189119999999</v>
+        <v>3.363285759999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1177105220037351</v>
+        <v>0.1186437582895535</v>
       </c>
       <c r="T35">
-        <v>0.7874496903326828</v>
+        <v>0.7976690101734806</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.192142565908947</v>
+        <v>2.127667784558684</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0989224804711053</v>
+        <v>0.09896771119970808</v>
       </c>
       <c r="C36">
-        <v>52.46106538056655</v>
+        <v>51.6718416270852</v>
       </c>
       <c r="D36">
-        <v>76.66906538056655</v>
+        <v>76.6038416270852</v>
       </c>
       <c r="E36">
-        <v>5.216000000000005</v>
+        <v>5.940000000000005</v>
       </c>
       <c r="F36">
-        <v>24.616</v>
+        <v>25.34</v>
       </c>
       <c r="G36">
         <v>0.408</v>
@@ -4361,28 +4361,28 @@
         <v>3.97</v>
       </c>
       <c r="M36">
-        <v>1.8658928</v>
+        <v>1.920772</v>
       </c>
       <c r="N36">
-        <v>2.1041072</v>
+        <v>2.049227999999999</v>
       </c>
       <c r="O36">
-        <v>0.4208214399999999</v>
+        <v>0.4098455999999999</v>
       </c>
       <c r="P36">
-        <v>1.68328576</v>
+        <v>1.639382399999999</v>
       </c>
       <c r="Q36">
-        <v>3.363285759999999</v>
+        <v>3.319382399999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1186437582895535</v>
+        <v>0.1196057095380124</v>
       </c>
       <c r="T36">
-        <v>0.7976690101734806</v>
+        <v>0.8082027706247646</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.127667784558684</v>
+        <v>2.066877276428436</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09896771119970808</v>
+        <v>0.09901294192831087</v>
       </c>
       <c r="C37">
-        <v>51.6718416270852</v>
+        <v>50.88272875331788</v>
       </c>
       <c r="D37">
-        <v>76.6038416270852</v>
+        <v>76.53872875331788</v>
       </c>
       <c r="E37">
-        <v>5.940000000000005</v>
+        <v>6.664000000000005</v>
       </c>
       <c r="F37">
-        <v>25.34</v>
+        <v>26.064</v>
       </c>
       <c r="G37">
         <v>0.408</v>
@@ -4443,28 +4443,28 @@
         <v>3.97</v>
       </c>
       <c r="M37">
-        <v>1.920772</v>
+        <v>1.9756512</v>
       </c>
       <c r="N37">
-        <v>2.049227999999999</v>
+        <v>1.994348799999999</v>
       </c>
       <c r="O37">
-        <v>0.4098455999999999</v>
+        <v>0.3988697599999999</v>
       </c>
       <c r="P37">
-        <v>1.639382399999999</v>
+        <v>1.595479039999999</v>
       </c>
       <c r="Q37">
-        <v>3.319382399999999</v>
+        <v>3.275479039999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1196057095380124</v>
+        <v>0.1205977217629857</v>
       </c>
       <c r="T37">
-        <v>0.8082027706247646</v>
+        <v>0.8190657110901512</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.066877276428436</v>
+        <v>2.009464018749868</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09901294192831087</v>
+        <v>0.1032613726569137</v>
       </c>
       <c r="C38">
-        <v>50.88272875331788</v>
+        <v>44.49980568676868</v>
       </c>
       <c r="D38">
-        <v>76.53872875331788</v>
+        <v>70.87980568676868</v>
       </c>
       <c r="E38">
-        <v>6.664000000000001</v>
+        <v>7.388000000000002</v>
       </c>
       <c r="F38">
-        <v>26.064</v>
+        <v>26.788</v>
       </c>
       <c r="G38">
         <v>0.408</v>
@@ -4525,45 +4525,45 @@
         <v>3.97</v>
       </c>
       <c r="M38">
-        <v>1.9756512</v>
+        <v>2.41092</v>
       </c>
       <c r="N38">
-        <v>1.9943488</v>
+        <v>1.55908</v>
       </c>
       <c r="O38">
-        <v>0.39886976</v>
+        <v>0.311816</v>
       </c>
       <c r="P38">
-        <v>1.59547904</v>
+        <v>1.247264</v>
       </c>
       <c r="Q38">
-        <v>3.27547904</v>
+        <v>2.927264</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1205977217629857</v>
+        <v>0.1216212264395455</v>
       </c>
       <c r="T38">
-        <v>0.8190657110901511</v>
+        <v>0.8302735068084073</v>
       </c>
       <c r="U38">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.009464018749868</v>
+        <v>1.646674298608</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1032613726569137</v>
+        <v>0.1034202033855164</v>
       </c>
       <c r="C39">
-        <v>44.49980568676868</v>
+        <v>43.58042471761225</v>
       </c>
       <c r="D39">
-        <v>70.87980568676868</v>
+        <v>70.68442471761225</v>
       </c>
       <c r="E39">
-        <v>7.388000000000002</v>
+        <v>8.112000000000005</v>
       </c>
       <c r="F39">
-        <v>26.788</v>
+        <v>27.512</v>
       </c>
       <c r="G39">
         <v>0.408</v>
@@ -4607,28 +4607,28 @@
         <v>3.97</v>
       </c>
       <c r="M39">
-        <v>2.41092</v>
+        <v>2.47608</v>
       </c>
       <c r="N39">
-        <v>1.55908</v>
+        <v>1.49392</v>
       </c>
       <c r="O39">
-        <v>0.311816</v>
+        <v>0.2987839999999999</v>
       </c>
       <c r="P39">
-        <v>1.247264</v>
+        <v>1.195136</v>
       </c>
       <c r="Q39">
-        <v>2.927264</v>
+        <v>2.875135999999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1216212264395455</v>
+        <v>0.1226777473959942</v>
       </c>
       <c r="T39">
-        <v>0.8302735068084073</v>
+        <v>0.8418428443240263</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.646674298608</v>
+        <v>1.603340764434105</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1034202033855164</v>
+        <v>0.1035790341141192</v>
       </c>
       <c r="C40">
-        <v>43.58042471761225</v>
+        <v>42.66211792708002</v>
       </c>
       <c r="D40">
-        <v>70.68442471761225</v>
+        <v>70.49011792708002</v>
       </c>
       <c r="E40">
-        <v>8.112000000000005</v>
+        <v>8.836000000000006</v>
       </c>
       <c r="F40">
-        <v>27.512</v>
+        <v>28.236</v>
       </c>
       <c r="G40">
         <v>0.408</v>
@@ -4689,28 +4689,28 @@
         <v>3.97</v>
       </c>
       <c r="M40">
-        <v>2.47608</v>
+        <v>2.54124</v>
       </c>
       <c r="N40">
-        <v>1.49392</v>
+        <v>1.42876</v>
       </c>
       <c r="O40">
-        <v>0.2987839999999999</v>
+        <v>0.285752</v>
       </c>
       <c r="P40">
-        <v>1.195136</v>
+        <v>1.143008</v>
       </c>
       <c r="Q40">
-        <v>2.875135999999999</v>
+        <v>2.823007999999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1226777473959942</v>
+        <v>0.123768908383802</v>
       </c>
       <c r="T40">
-        <v>0.8418428443240263</v>
+        <v>0.8537915043811413</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.603340764434105</v>
+        <v>1.562229462781949</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1035790341141192</v>
+        <v>0.103737864842722</v>
       </c>
       <c r="C41">
-        <v>42.66211792708002</v>
+        <v>41.7448764809196</v>
       </c>
       <c r="D41">
-        <v>70.49011792708002</v>
+        <v>70.29687648091961</v>
       </c>
       <c r="E41">
-        <v>8.836000000000006</v>
+        <v>9.560000000000006</v>
       </c>
       <c r="F41">
-        <v>28.236</v>
+        <v>28.96</v>
       </c>
       <c r="G41">
         <v>0.408</v>
@@ -4771,28 +4771,28 @@
         <v>3.97</v>
       </c>
       <c r="M41">
-        <v>2.54124</v>
+        <v>2.6064</v>
       </c>
       <c r="N41">
-        <v>1.42876</v>
+        <v>1.363599999999999</v>
       </c>
       <c r="O41">
-        <v>0.285752</v>
+        <v>0.2727199999999999</v>
       </c>
       <c r="P41">
-        <v>1.143008</v>
+        <v>1.09088</v>
       </c>
       <c r="Q41">
-        <v>2.823007999999999</v>
+        <v>2.770879999999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.123768908383802</v>
+        <v>0.1248964414045367</v>
       </c>
       <c r="T41">
-        <v>0.8537915043811413</v>
+        <v>0.8661384531068266</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.562229462781949</v>
+        <v>1.5231737262124</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.103737864842722</v>
+        <v>0.1239740995513461</v>
       </c>
       <c r="C42">
-        <v>41.7448764809196</v>
+        <v>22.823748532977</v>
       </c>
       <c r="D42">
-        <v>70.29687648091961</v>
+        <v>52.099748532977</v>
       </c>
       <c r="E42">
-        <v>9.560000000000006</v>
+        <v>10.28400000000001</v>
       </c>
       <c r="F42">
-        <v>28.96</v>
+        <v>29.684</v>
       </c>
       <c r="G42">
         <v>0.408</v>
@@ -4853,45 +4853,45 @@
         <v>3.97</v>
       </c>
       <c r="M42">
-        <v>2.6064</v>
+        <v>4.357611200000001</v>
       </c>
       <c r="N42">
-        <v>1.363599999999999</v>
+        <v>-0.3876112000000012</v>
       </c>
       <c r="O42">
-        <v>0.2727199999999999</v>
+        <v>-0.07752224000000024</v>
       </c>
       <c r="P42">
-        <v>1.09088</v>
+        <v>-0.3100889600000009</v>
       </c>
       <c r="Q42">
-        <v>2.770879999999999</v>
+        <v>1.369911039999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1248964414045367</v>
+        <v>0.1266999158984328</v>
       </c>
       <c r="T42">
-        <v>0.8661384531068266</v>
+        <v>0.8858872380157677</v>
       </c>
       <c r="U42">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.2</v>
+        <v>0.1822099227209623</v>
       </c>
       <c r="W42">
-        <v>0.07199999999999999</v>
+        <v>0.1200515833445627</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.5231737262124</v>
+        <v>0.9110496136048115</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1239740995513461</v>
+        <v>0.1249840995513461</v>
       </c>
       <c r="C43">
-        <v>22.823748532977</v>
+        <v>21.43521175960388</v>
       </c>
       <c r="D43">
-        <v>52.099748532977</v>
+        <v>51.43521175960389</v>
       </c>
       <c r="E43">
-        <v>10.28400000000001</v>
+        <v>11.00800000000001</v>
       </c>
       <c r="F43">
-        <v>29.684</v>
+        <v>30.408</v>
       </c>
       <c r="G43">
         <v>0.408</v>
@@ -4935,37 +4935,37 @@
         <v>3.97</v>
       </c>
       <c r="M43">
-        <v>4.357611200000001</v>
+        <v>4.463894400000001</v>
       </c>
       <c r="N43">
-        <v>-0.3876112000000012</v>
+        <v>-0.4938944000000012</v>
       </c>
       <c r="O43">
-        <v>-0.07752224000000024</v>
+        <v>-0.09877888000000024</v>
       </c>
       <c r="P43">
-        <v>-0.3100889600000009</v>
+        <v>-0.3951155200000009</v>
       </c>
       <c r="Q43">
-        <v>1.369911039999999</v>
+        <v>1.284884479999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1266999158984328</v>
+        <v>0.1280947420346127</v>
       </c>
       <c r="T43">
-        <v>0.8858872380157677</v>
+        <v>0.9011611559125914</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1822099227209623</v>
+        <v>0.1778715912276061</v>
       </c>
       <c r="W43">
-        <v>0.1200515833445627</v>
+        <v>0.1206884504077874</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.9110496136048115</v>
+        <v>0.8893579561380303</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1249840995513461</v>
+        <v>0.1259940995513461</v>
       </c>
       <c r="C44">
-        <v>21.43521175960388</v>
+        <v>20.06341392699727</v>
       </c>
       <c r="D44">
-        <v>51.43521175960388</v>
+        <v>50.78741392699727</v>
       </c>
       <c r="E44">
-        <v>11.008</v>
+        <v>11.732</v>
       </c>
       <c r="F44">
-        <v>30.408</v>
+        <v>31.132</v>
       </c>
       <c r="G44">
         <v>0.408</v>
@@ -5017,37 +5017,37 @@
         <v>3.97</v>
       </c>
       <c r="M44">
-        <v>4.463894400000001</v>
+        <v>4.570177600000001</v>
       </c>
       <c r="N44">
-        <v>-0.4938944000000012</v>
+        <v>-0.6001776000000012</v>
       </c>
       <c r="O44">
-        <v>-0.09877888000000024</v>
+        <v>-0.1200355200000002</v>
       </c>
       <c r="P44">
-        <v>-0.3951155200000009</v>
+        <v>-0.480142080000001</v>
       </c>
       <c r="Q44">
-        <v>1.284884479999999</v>
+        <v>1.199857919999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1280947420346127</v>
+        <v>0.1295385094387287</v>
       </c>
       <c r="T44">
-        <v>0.9011611559125914</v>
+        <v>0.9169710007531631</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.1778715912276061</v>
+        <v>0.1737350425944059</v>
       </c>
       <c r="W44">
-        <v>0.1206884504077874</v>
+        <v>0.1212956957471412</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8893579561380303</v>
+        <v>0.8686752129720295</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1259940995513461</v>
+        <v>0.1270040995513461</v>
       </c>
       <c r="C45">
-        <v>20.06341392699727</v>
+        <v>18.70773044858088</v>
       </c>
       <c r="D45">
-        <v>50.78741392699727</v>
+        <v>50.15573044858088</v>
       </c>
       <c r="E45">
-        <v>11.732</v>
+        <v>12.456</v>
       </c>
       <c r="F45">
-        <v>31.132</v>
+        <v>31.856</v>
       </c>
       <c r="G45">
         <v>0.408</v>
@@ -5099,37 +5099,37 @@
         <v>3.97</v>
       </c>
       <c r="M45">
-        <v>4.570177600000001</v>
+        <v>4.676460800000001</v>
       </c>
       <c r="N45">
-        <v>-0.6001776000000012</v>
+        <v>-0.7064608000000012</v>
       </c>
       <c r="O45">
-        <v>-0.1200355200000002</v>
+        <v>-0.1412921600000002</v>
       </c>
       <c r="P45">
-        <v>-0.480142080000001</v>
+        <v>-0.565168640000001</v>
       </c>
       <c r="Q45">
-        <v>1.199857919999999</v>
+        <v>1.114831359999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1295385094387287</v>
+        <v>0.1310338399644203</v>
       </c>
       <c r="T45">
-        <v>0.9169710007531631</v>
+        <v>0.9333454829094696</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.1737350425944059</v>
+        <v>0.1697865188990785</v>
       </c>
       <c r="W45">
-        <v>0.1212956957471412</v>
+        <v>0.1218753390256153</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8686752129720295</v>
+        <v>0.8489325944953925</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1270040995513461</v>
+        <v>0.1280140995513461</v>
       </c>
       <c r="C46">
-        <v>18.70773044858088</v>
+        <v>17.36756742995618</v>
       </c>
       <c r="D46">
-        <v>50.15573044858088</v>
+        <v>49.53956742995619</v>
       </c>
       <c r="E46">
-        <v>12.456</v>
+        <v>13.18000000000001</v>
       </c>
       <c r="F46">
-        <v>31.856</v>
+        <v>32.58000000000001</v>
       </c>
       <c r="G46">
         <v>0.408</v>
@@ -5181,37 +5181,37 @@
         <v>3.97</v>
       </c>
       <c r="M46">
-        <v>4.676460800000001</v>
+        <v>4.782744000000001</v>
       </c>
       <c r="N46">
-        <v>-0.7064608000000012</v>
+        <v>-0.8127440000000012</v>
       </c>
       <c r="O46">
-        <v>-0.1412921600000002</v>
+        <v>-0.1625488000000003</v>
       </c>
       <c r="P46">
-        <v>-0.565168640000001</v>
+        <v>-0.650195200000001</v>
       </c>
       <c r="Q46">
-        <v>1.114831359999999</v>
+        <v>1.029804799999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1310338399644203</v>
+        <v>0.1325835461455916</v>
       </c>
       <c r="T46">
-        <v>0.9333454829094696</v>
+        <v>0.9503154007805509</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1697865188990785</v>
+        <v>0.1660134851457657</v>
       </c>
       <c r="W46">
-        <v>0.1218753390256153</v>
+        <v>0.1224292203806016</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8489325944953925</v>
+        <v>0.8300674257288283</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1280140995513461</v>
+        <v>0.1290240995513461</v>
       </c>
       <c r="C47">
-        <v>17.36756742995618</v>
+        <v>16.04235980651553</v>
       </c>
       <c r="D47">
-        <v>49.53956742995619</v>
+        <v>48.93835980651553</v>
       </c>
       <c r="E47">
-        <v>13.18000000000001</v>
+        <v>13.904</v>
       </c>
       <c r="F47">
-        <v>32.58000000000001</v>
+        <v>33.304</v>
       </c>
       <c r="G47">
         <v>0.408</v>
@@ -5263,37 +5263,37 @@
         <v>3.97</v>
       </c>
       <c r="M47">
-        <v>4.782744000000001</v>
+        <v>4.889027200000001</v>
       </c>
       <c r="N47">
-        <v>-0.8127440000000012</v>
+        <v>-0.9190272000000013</v>
       </c>
       <c r="O47">
-        <v>-0.1625488000000003</v>
+        <v>-0.1838054400000003</v>
       </c>
       <c r="P47">
-        <v>-0.650195200000001</v>
+        <v>-0.7352217600000011</v>
       </c>
       <c r="Q47">
-        <v>1.029804799999999</v>
+        <v>0.9447782399999987</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1325835461455916</v>
+        <v>0.1341906488519914</v>
       </c>
       <c r="T47">
-        <v>0.9503154007805509</v>
+        <v>0.9679138341283389</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1660134851457657</v>
+        <v>0.162404496338249</v>
       </c>
       <c r="W47">
-        <v>0.1224292203806016</v>
+        <v>0.122959019937545</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8300674257288283</v>
+        <v>0.812022481691245</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1290240995513461</v>
+        <v>0.1564504491888009</v>
       </c>
       <c r="C48">
-        <v>16.04235980651553</v>
+        <v>3.188263845975079</v>
       </c>
       <c r="D48">
-        <v>48.93835980651553</v>
+        <v>36.80826384597508</v>
       </c>
       <c r="E48">
-        <v>13.904</v>
+        <v>14.62800000000001</v>
       </c>
       <c r="F48">
-        <v>33.304</v>
+        <v>34.02800000000001</v>
       </c>
       <c r="G48">
         <v>0.408</v>
@@ -5345,45 +5345,45 @@
         <v>3.97</v>
       </c>
       <c r="M48">
-        <v>4.889027200000001</v>
+        <v>6.832822400000001</v>
       </c>
       <c r="N48">
-        <v>-0.9190272000000013</v>
+        <v>-2.862822400000002</v>
       </c>
       <c r="O48">
-        <v>-0.1838054400000003</v>
+        <v>-0.5725644800000004</v>
       </c>
       <c r="P48">
-        <v>-0.7352217600000011</v>
+        <v>-2.290257920000001</v>
       </c>
       <c r="Q48">
-        <v>0.9447782399999987</v>
+        <v>-0.6102579200000013</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1341906488519914</v>
+        <v>0.1378137736179814</v>
       </c>
       <c r="T48">
-        <v>0.9679138341283389</v>
+        <v>1.007588535347547</v>
       </c>
       <c r="U48">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.162404496338249</v>
+        <v>0.1162038105951649</v>
       </c>
       <c r="W48">
-        <v>0.122959019937545</v>
+        <v>0.1774662748324909</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.812022481691245</v>
+        <v>0.5810190529758243</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1564504491888009</v>
+        <v>0.1580004491888009</v>
       </c>
       <c r="C49">
-        <v>3.188263845975079</v>
+        <v>1.955773823218955</v>
       </c>
       <c r="D49">
-        <v>36.80826384597508</v>
+        <v>36.29977382321896</v>
       </c>
       <c r="E49">
-        <v>14.62800000000001</v>
+        <v>15.352</v>
       </c>
       <c r="F49">
-        <v>34.02800000000001</v>
+        <v>34.752</v>
       </c>
       <c r="G49">
         <v>0.408</v>
@@ -5427,37 +5427,37 @@
         <v>3.97</v>
       </c>
       <c r="M49">
-        <v>6.832822400000001</v>
+        <v>6.978201600000001</v>
       </c>
       <c r="N49">
-        <v>-2.862822400000002</v>
+        <v>-3.008201600000001</v>
       </c>
       <c r="O49">
-        <v>-0.5725644800000004</v>
+        <v>-0.6016403200000003</v>
       </c>
       <c r="P49">
-        <v>-2.290257920000001</v>
+        <v>-2.406561280000001</v>
       </c>
       <c r="Q49">
-        <v>-0.6102579200000013</v>
+        <v>-0.7265612800000012</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1378137736179814</v>
+        <v>0.139583269264481</v>
       </c>
       <c r="T49">
-        <v>1.007588535347547</v>
+        <v>1.026965237950384</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1162038105951649</v>
+        <v>0.1137828978744323</v>
       </c>
       <c r="W49">
-        <v>0.1774662748324909</v>
+        <v>0.177952394106814</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5810190529758243</v>
+        <v>0.5689144893721614</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1580004491888009</v>
+        <v>0.1595504491888008</v>
       </c>
       <c r="C50">
-        <v>1.955773823218955</v>
+        <v>0.7371414958107181</v>
       </c>
       <c r="D50">
-        <v>36.29977382321896</v>
+        <v>35.80514149581072</v>
       </c>
       <c r="E50">
-        <v>15.352</v>
+        <v>16.076</v>
       </c>
       <c r="F50">
-        <v>34.752</v>
+        <v>35.476</v>
       </c>
       <c r="G50">
         <v>0.408</v>
@@ -5509,37 +5509,37 @@
         <v>3.97</v>
       </c>
       <c r="M50">
-        <v>6.978201600000001</v>
+        <v>7.1235808</v>
       </c>
       <c r="N50">
-        <v>-3.008201600000001</v>
+        <v>-3.1535808</v>
       </c>
       <c r="O50">
-        <v>-0.6016403200000003</v>
+        <v>-0.6307161600000001</v>
       </c>
       <c r="P50">
-        <v>-2.406561280000001</v>
+        <v>-2.52286464</v>
       </c>
       <c r="Q50">
-        <v>-0.7265612800000012</v>
+        <v>-0.8428646400000006</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.139583269264481</v>
+        <v>0.1414221568971179</v>
       </c>
       <c r="T50">
-        <v>1.026965237950384</v>
+        <v>1.047101811243529</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1137828978744323</v>
+        <v>0.1114607979178112</v>
       </c>
       <c r="W50">
-        <v>0.177952394106814</v>
+        <v>0.1784186717781035</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5689144893721614</v>
+        <v>0.5573039895890561</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1595504491888008</v>
+        <v>0.1611004491888008</v>
       </c>
       <c r="C51">
-        <v>0.7371414958107181</v>
+        <v>-0.468192009036521</v>
       </c>
       <c r="D51">
-        <v>35.80514149581072</v>
+        <v>35.32380799096348</v>
       </c>
       <c r="E51">
-        <v>16.076</v>
+        <v>16.8</v>
       </c>
       <c r="F51">
-        <v>35.476</v>
+        <v>36.2</v>
       </c>
       <c r="G51">
         <v>0.408</v>
@@ -5591,37 +5591,37 @@
         <v>3.97</v>
       </c>
       <c r="M51">
-        <v>7.1235808</v>
+        <v>7.268960000000001</v>
       </c>
       <c r="N51">
-        <v>-3.1535808</v>
+        <v>-3.298960000000001</v>
       </c>
       <c r="O51">
-        <v>-0.6307161600000001</v>
+        <v>-0.6597920000000003</v>
       </c>
       <c r="P51">
-        <v>-2.52286464</v>
+        <v>-2.639168000000001</v>
       </c>
       <c r="Q51">
-        <v>-0.8428646400000006</v>
+        <v>-0.9591680000000009</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1414221568971179</v>
+        <v>0.1433346000350603</v>
       </c>
       <c r="T51">
-        <v>1.047101811243529</v>
+        <v>1.0680438474684</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1114607979178112</v>
+        <v>0.109231581959455</v>
       </c>
       <c r="W51">
-        <v>0.1784186717781035</v>
+        <v>0.1788662983425414</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5573039895890561</v>
+        <v>0.5461579097972749</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1611004491888008</v>
+        <v>0.1626504491888009</v>
       </c>
       <c r="C52">
-        <v>-0.468192009036521</v>
+        <v>-1.660755910725335</v>
       </c>
       <c r="D52">
-        <v>35.32380799096348</v>
+        <v>34.85524408927467</v>
       </c>
       <c r="E52">
-        <v>16.8</v>
+        <v>17.52400000000001</v>
       </c>
       <c r="F52">
-        <v>36.2</v>
+        <v>36.92400000000001</v>
       </c>
       <c r="G52">
         <v>0.408</v>
@@ -5673,37 +5673,37 @@
         <v>3.97</v>
       </c>
       <c r="M52">
-        <v>7.268960000000001</v>
+        <v>7.414339200000001</v>
       </c>
       <c r="N52">
-        <v>-3.298960000000001</v>
+        <v>-3.444339200000002</v>
       </c>
       <c r="O52">
-        <v>-0.6597920000000003</v>
+        <v>-0.6888678400000003</v>
       </c>
       <c r="P52">
-        <v>-2.639168000000001</v>
+        <v>-2.755471360000001</v>
       </c>
       <c r="Q52">
-        <v>-0.9591680000000009</v>
+        <v>-1.075471360000002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1433346000350603</v>
+        <v>0.1453251020765921</v>
       </c>
       <c r="T52">
-        <v>1.0680438474684</v>
+        <v>1.08984066068204</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.109231581959455</v>
+        <v>0.1070897862347598</v>
       </c>
       <c r="W52">
-        <v>0.1788662983425414</v>
+        <v>0.1792963709240603</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5461579097972749</v>
+        <v>0.5354489311737989</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1626504491888009</v>
+        <v>0.1642004491888008</v>
       </c>
       <c r="C53">
-        <v>-1.660755910725335</v>
+        <v>-2.841051716260878</v>
       </c>
       <c r="D53">
-        <v>34.85524408927467</v>
+        <v>34.39894828373912</v>
       </c>
       <c r="E53">
-        <v>17.52400000000001</v>
+        <v>18.248</v>
       </c>
       <c r="F53">
-        <v>36.92400000000001</v>
+        <v>37.648</v>
       </c>
       <c r="G53">
         <v>0.408</v>
@@ -5755,37 +5755,37 @@
         <v>3.97</v>
       </c>
       <c r="M53">
-        <v>7.414339200000001</v>
+        <v>7.559718400000001</v>
       </c>
       <c r="N53">
-        <v>-3.444339200000002</v>
+        <v>-3.589718400000002</v>
       </c>
       <c r="O53">
-        <v>-0.6888678400000003</v>
+        <v>-0.7179436800000003</v>
       </c>
       <c r="P53">
-        <v>-2.755471360000001</v>
+        <v>-2.871774720000001</v>
       </c>
       <c r="Q53">
-        <v>-1.075471360000002</v>
+        <v>-1.191774720000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1453251020765921</v>
+        <v>0.1473985417031878</v>
       </c>
       <c r="T53">
-        <v>1.08984066068204</v>
+        <v>1.11254567444625</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1070897862347598</v>
+        <v>0.1050303672687067</v>
       </c>
       <c r="W53">
-        <v>0.1792963709240603</v>
+        <v>0.1797099022524437</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5354489311737989</v>
+        <v>0.5251518363435335</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1642004491888008</v>
+        <v>0.1657504491888009</v>
       </c>
       <c r="C54">
-        <v>-2.841051716260878</v>
+        <v>-4.009555010749381</v>
       </c>
       <c r="D54">
-        <v>34.39894828373912</v>
+        <v>33.95444498925063</v>
       </c>
       <c r="E54">
-        <v>18.248</v>
+        <v>18.97200000000001</v>
       </c>
       <c r="F54">
-        <v>37.648</v>
+        <v>38.37200000000001</v>
       </c>
       <c r="G54">
         <v>0.408</v>
@@ -5837,37 +5837,37 @@
         <v>3.97</v>
       </c>
       <c r="M54">
-        <v>7.559718400000001</v>
+        <v>7.705097600000002</v>
       </c>
       <c r="N54">
-        <v>-3.589718400000002</v>
+        <v>-3.735097600000002</v>
       </c>
       <c r="O54">
-        <v>-0.7179436800000003</v>
+        <v>-0.7470195200000005</v>
       </c>
       <c r="P54">
-        <v>-2.871774720000001</v>
+        <v>-2.988078080000002</v>
       </c>
       <c r="Q54">
-        <v>-1.191774720000002</v>
+        <v>-1.308078080000002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1473985417031878</v>
+        <v>0.1495602128032556</v>
       </c>
       <c r="T54">
-        <v>1.11254567444625</v>
+        <v>1.136216859008936</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1050303672687067</v>
+        <v>0.1030486622259009</v>
       </c>
       <c r="W54">
-        <v>0.1797099022524437</v>
+        <v>0.1801078286250391</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5251518363435335</v>
+        <v>0.5152433111295045</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1657504491888009</v>
+        <v>0.1673004491888008</v>
       </c>
       <c r="C55">
-        <v>-4.009555010749381</v>
+        <v>-5.166717110846271</v>
       </c>
       <c r="D55">
-        <v>33.95444498925063</v>
+        <v>33.52128288915373</v>
       </c>
       <c r="E55">
-        <v>18.97200000000001</v>
+        <v>19.69600000000001</v>
       </c>
       <c r="F55">
-        <v>38.37200000000001</v>
+        <v>39.096</v>
       </c>
       <c r="G55">
         <v>0.408</v>
@@ -5919,37 +5919,37 @@
         <v>3.97</v>
       </c>
       <c r="M55">
-        <v>7.705097600000002</v>
+        <v>7.850476800000001</v>
       </c>
       <c r="N55">
-        <v>-3.735097600000002</v>
+        <v>-3.880476800000001</v>
       </c>
       <c r="O55">
-        <v>-0.7470195200000005</v>
+        <v>-0.7760953600000002</v>
       </c>
       <c r="P55">
-        <v>-2.988078080000002</v>
+        <v>-3.104381440000001</v>
       </c>
       <c r="Q55">
-        <v>-1.308078080000002</v>
+        <v>-1.424381440000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1495602128032556</v>
+        <v>0.1518158696033264</v>
       </c>
       <c r="T55">
-        <v>1.136216859008936</v>
+        <v>1.16091722550913</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1030486622259009</v>
+        <v>0.101140353666162</v>
       </c>
       <c r="W55">
-        <v>0.1801078286250391</v>
+        <v>0.1804910169838347</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5152433111295045</v>
+        <v>0.50570176833081</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1673004491888008</v>
+        <v>0.1885186287852293</v>
       </c>
       <c r="C56">
-        <v>-5.166717110846271</v>
+        <v>-10.87437346109815</v>
       </c>
       <c r="D56">
-        <v>33.52128288915373</v>
+        <v>28.53762653890186</v>
       </c>
       <c r="E56">
-        <v>19.69600000000001</v>
+        <v>20.42000000000001</v>
       </c>
       <c r="F56">
-        <v>39.096</v>
+        <v>39.82000000000001</v>
       </c>
       <c r="G56">
         <v>0.408</v>
@@ -6001,45 +6001,45 @@
         <v>3.97</v>
       </c>
       <c r="M56">
-        <v>7.850476800000001</v>
+        <v>9.389556000000002</v>
       </c>
       <c r="N56">
-        <v>-3.880476800000001</v>
+        <v>-5.419556000000003</v>
       </c>
       <c r="O56">
-        <v>-0.7760953600000002</v>
+        <v>-1.083911200000001</v>
       </c>
       <c r="P56">
-        <v>-3.104381440000001</v>
+        <v>-4.335644800000003</v>
       </c>
       <c r="Q56">
-        <v>-1.424381440000001</v>
+        <v>-2.655644800000003</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1518158696033264</v>
+        <v>0.1551010658087968</v>
       </c>
       <c r="T56">
-        <v>1.16091722550913</v>
+        <v>1.196891470481867</v>
       </c>
       <c r="U56">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.101140353666162</v>
+        <v>0.08456203892921027</v>
       </c>
       <c r="W56">
-        <v>0.1804910169838347</v>
+        <v>0.2158602712204922</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.50570176833081</v>
+        <v>0.4228101946460513</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1885186287852293</v>
+        <v>0.1904186287852293</v>
       </c>
       <c r="C57">
-        <v>-10.87437346109815</v>
+        <v>-11.97330088835538</v>
       </c>
       <c r="D57">
-        <v>28.53762653890186</v>
+        <v>28.16269911164463</v>
       </c>
       <c r="E57">
-        <v>20.42000000000001</v>
+        <v>21.14400000000001</v>
       </c>
       <c r="F57">
-        <v>39.82000000000001</v>
+        <v>40.544</v>
       </c>
       <c r="G57">
         <v>0.408</v>
@@ -6083,37 +6083,37 @@
         <v>3.97</v>
       </c>
       <c r="M57">
-        <v>9.389556000000002</v>
+        <v>9.560275200000001</v>
       </c>
       <c r="N57">
-        <v>-5.419556000000003</v>
+        <v>-5.590275200000002</v>
       </c>
       <c r="O57">
-        <v>-1.083911200000001</v>
+        <v>-1.11805504</v>
       </c>
       <c r="P57">
-        <v>-4.335644800000003</v>
+        <v>-4.472220160000001</v>
       </c>
       <c r="Q57">
-        <v>-2.655644800000003</v>
+        <v>-2.792220160000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1551010658087968</v>
+        <v>0.1575851809408149</v>
       </c>
       <c r="T57">
-        <v>1.196891470481867</v>
+        <v>1.224093549356455</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.08456203892921027</v>
+        <v>0.08305200251976008</v>
       </c>
       <c r="W57">
-        <v>0.2158602712204922</v>
+        <v>0.2162163378058406</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4228101946460513</v>
+        <v>0.4152600125988004</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1904186287852293</v>
+        <v>0.1923186287852293</v>
       </c>
       <c r="C58">
-        <v>-11.97330088835538</v>
+        <v>-13.06250447206186</v>
       </c>
       <c r="D58">
-        <v>28.16269911164463</v>
+        <v>27.79749552793815</v>
       </c>
       <c r="E58">
-        <v>21.14400000000001</v>
+        <v>21.86800000000001</v>
       </c>
       <c r="F58">
-        <v>40.544</v>
+        <v>41.26800000000001</v>
       </c>
       <c r="G58">
         <v>0.408</v>
@@ -6165,37 +6165,37 @@
         <v>3.97</v>
       </c>
       <c r="M58">
-        <v>9.560275200000001</v>
+        <v>9.730994400000002</v>
       </c>
       <c r="N58">
-        <v>-5.590275200000002</v>
+        <v>-5.760994400000002</v>
       </c>
       <c r="O58">
-        <v>-1.11805504</v>
+        <v>-1.15219888</v>
       </c>
       <c r="P58">
-        <v>-4.472220160000001</v>
+        <v>-4.608795520000002</v>
       </c>
       <c r="Q58">
-        <v>-2.792220160000001</v>
+        <v>-2.928795520000002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1575851809408149</v>
+        <v>0.1601848363115316</v>
       </c>
       <c r="T58">
-        <v>1.224093549356455</v>
+        <v>1.252560841201955</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.08305200251976008</v>
+        <v>0.08159494984397482</v>
       </c>
       <c r="W58">
-        <v>0.2162163378058406</v>
+        <v>0.2165599108267907</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4152600125988004</v>
+        <v>0.4079747492198741</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1923186287852293</v>
+        <v>0.1942186287852293</v>
       </c>
       <c r="C59">
-        <v>-13.06250447206186</v>
+        <v>-14.14235765528665</v>
       </c>
       <c r="D59">
-        <v>27.79749552793815</v>
+        <v>27.44164234471336</v>
       </c>
       <c r="E59">
-        <v>21.86800000000001</v>
+        <v>22.59200000000001</v>
       </c>
       <c r="F59">
-        <v>41.26800000000001</v>
+        <v>41.99200000000001</v>
       </c>
       <c r="G59">
         <v>0.408</v>
@@ -6247,37 +6247,37 @@
         <v>3.97</v>
       </c>
       <c r="M59">
-        <v>9.730994400000002</v>
+        <v>9.901713600000003</v>
       </c>
       <c r="N59">
-        <v>-5.760994400000002</v>
+        <v>-5.931713600000003</v>
       </c>
       <c r="O59">
-        <v>-1.15219888</v>
+        <v>-1.186342720000001</v>
       </c>
       <c r="P59">
-        <v>-4.608795520000002</v>
+        <v>-4.745370880000002</v>
       </c>
       <c r="Q59">
-        <v>-2.928795520000002</v>
+        <v>-3.065370880000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1601848363115316</v>
+        <v>0.1629082847951395</v>
       </c>
       <c r="T59">
-        <v>1.252560841201955</v>
+        <v>1.28238371837343</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08159494984397482</v>
+        <v>0.08018814036390629</v>
       </c>
       <c r="W59">
-        <v>0.2165599108267907</v>
+        <v>0.2168916365021909</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4079747492198741</v>
+        <v>0.4009407018195313</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1942186287852293</v>
+        <v>0.1961186287852293</v>
       </c>
       <c r="C60">
-        <v>-14.14235765528663</v>
+        <v>-15.21321500009019</v>
       </c>
       <c r="D60">
-        <v>27.44164234471337</v>
+        <v>27.09478499990981</v>
       </c>
       <c r="E60">
-        <v>22.592</v>
+        <v>23.316</v>
       </c>
       <c r="F60">
-        <v>41.992</v>
+        <v>42.716</v>
       </c>
       <c r="G60">
         <v>0.408</v>
@@ -6329,37 +6329,37 @@
         <v>3.97</v>
       </c>
       <c r="M60">
-        <v>9.901713599999999</v>
+        <v>10.0724328</v>
       </c>
       <c r="N60">
-        <v>-5.931713599999999</v>
+        <v>-6.102432800000002</v>
       </c>
       <c r="O60">
-        <v>-1.18634272</v>
+        <v>-1.22048656</v>
       </c>
       <c r="P60">
-        <v>-4.745370879999999</v>
+        <v>-4.881946240000001</v>
       </c>
       <c r="Q60">
-        <v>-3.06537088</v>
+        <v>-3.201946240000002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1629082847951394</v>
+        <v>0.1657645844242892</v>
       </c>
       <c r="T60">
-        <v>1.282383718373429</v>
+        <v>1.313661370041074</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08018814036390631</v>
+        <v>0.07882901934078923</v>
       </c>
       <c r="W60">
-        <v>0.2168916365021909</v>
+        <v>0.2172121172394419</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4009407018195316</v>
+        <v>0.3941450967039462</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1961186287852293</v>
+        <v>0.1980186287852293</v>
       </c>
       <c r="C61">
-        <v>-15.21321500009019</v>
+        <v>-16.27541336589248</v>
       </c>
       <c r="D61">
-        <v>27.09478499990981</v>
+        <v>26.75658663410753</v>
       </c>
       <c r="E61">
-        <v>23.316</v>
+        <v>24.04000000000001</v>
       </c>
       <c r="F61">
-        <v>42.716</v>
+        <v>43.44</v>
       </c>
       <c r="G61">
         <v>0.408</v>
@@ -6411,37 +6411,37 @@
         <v>3.97</v>
       </c>
       <c r="M61">
-        <v>10.0724328</v>
+        <v>10.243152</v>
       </c>
       <c r="N61">
-        <v>-6.102432800000002</v>
+        <v>-6.273152000000002</v>
       </c>
       <c r="O61">
-        <v>-1.22048656</v>
+        <v>-1.254630400000001</v>
       </c>
       <c r="P61">
-        <v>-4.881946240000001</v>
+        <v>-5.018521600000001</v>
       </c>
       <c r="Q61">
-        <v>-3.201946240000002</v>
+        <v>-3.338521600000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1657645844242892</v>
+        <v>0.1687636990348964</v>
       </c>
       <c r="T61">
-        <v>1.313661370041074</v>
+        <v>1.346502904292101</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.07882901934078923</v>
+        <v>0.07751520235177607</v>
       </c>
       <c r="W61">
-        <v>0.2172121172394419</v>
+        <v>0.2175219152854512</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3941450967039462</v>
+        <v>0.3875760117588803</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1980186287852293</v>
+        <v>0.1999186287852293</v>
       </c>
       <c r="C62">
-        <v>-16.27541336589248</v>
+        <v>-17.32927300067841</v>
       </c>
       <c r="D62">
-        <v>26.75658663410753</v>
+        <v>26.42672699932159</v>
       </c>
       <c r="E62">
-        <v>24.04000000000001</v>
+        <v>24.764</v>
       </c>
       <c r="F62">
-        <v>43.44</v>
+        <v>44.164</v>
       </c>
       <c r="G62">
         <v>0.408</v>
@@ -6493,37 +6493,37 @@
         <v>3.97</v>
       </c>
       <c r="M62">
-        <v>10.243152</v>
+        <v>10.4138712</v>
       </c>
       <c r="N62">
-        <v>-6.273152000000002</v>
+        <v>-6.443871200000001</v>
       </c>
       <c r="O62">
-        <v>-1.254630400000001</v>
+        <v>-1.28877424</v>
       </c>
       <c r="P62">
-        <v>-5.018521600000001</v>
+        <v>-5.155096960000001</v>
       </c>
       <c r="Q62">
-        <v>-3.338521600000002</v>
+        <v>-3.475096960000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1687636990348964</v>
+        <v>0.1719166143947655</v>
       </c>
       <c r="T62">
-        <v>1.346502904292101</v>
+        <v>1.38102861978677</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07751520235177607</v>
+        <v>0.07624446132961582</v>
       </c>
       <c r="W62">
-        <v>0.2175219152854512</v>
+        <v>0.2178215560184766</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3875760117588803</v>
+        <v>0.3812223066480791</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1999186287852293</v>
+        <v>0.2018186287852293</v>
       </c>
       <c r="C63">
-        <v>-17.32927300067841</v>
+        <v>-18.37509855247087</v>
       </c>
       <c r="D63">
-        <v>26.42672699932159</v>
+        <v>26.10490144752913</v>
       </c>
       <c r="E63">
-        <v>24.764</v>
+        <v>25.48800000000001</v>
       </c>
       <c r="F63">
-        <v>44.164</v>
+        <v>44.88800000000001</v>
       </c>
       <c r="G63">
         <v>0.408</v>
@@ -6575,37 +6575,37 @@
         <v>3.97</v>
       </c>
       <c r="M63">
-        <v>10.4138712</v>
+        <v>10.5845904</v>
       </c>
       <c r="N63">
-        <v>-6.443871200000001</v>
+        <v>-6.614590400000002</v>
       </c>
       <c r="O63">
-        <v>-1.28877424</v>
+        <v>-1.32291808</v>
       </c>
       <c r="P63">
-        <v>-5.155096960000001</v>
+        <v>-5.291672320000002</v>
       </c>
       <c r="Q63">
-        <v>-3.475096960000001</v>
+        <v>-3.611672320000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1719166143947655</v>
+        <v>0.175235472668312</v>
       </c>
       <c r="T63">
-        <v>1.38102861978677</v>
+        <v>1.417371478202212</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.07624446132961582</v>
+        <v>0.0750147119533317</v>
       </c>
       <c r="W63">
-        <v>0.2178215560184766</v>
+        <v>0.2181115309214044</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3812223066480791</v>
+        <v>0.3750735597666585</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2018186287852293</v>
+        <v>0.2037186287852293</v>
       </c>
       <c r="C64">
-        <v>-18.37509855247087</v>
+        <v>-19.41318000778645</v>
       </c>
       <c r="D64">
-        <v>26.10490144752913</v>
+        <v>25.79081999221355</v>
       </c>
       <c r="E64">
-        <v>25.48800000000001</v>
+        <v>26.212</v>
       </c>
       <c r="F64">
-        <v>44.88800000000001</v>
+        <v>45.612</v>
       </c>
       <c r="G64">
         <v>0.408</v>
@@ -6657,37 +6657,37 @@
         <v>3.97</v>
       </c>
       <c r="M64">
-        <v>10.5845904</v>
+        <v>10.7553096</v>
       </c>
       <c r="N64">
-        <v>-6.614590400000002</v>
+        <v>-6.785309600000001</v>
       </c>
       <c r="O64">
-        <v>-1.32291808</v>
+        <v>-1.35706192</v>
       </c>
       <c r="P64">
-        <v>-5.291672320000002</v>
+        <v>-5.42824768</v>
       </c>
       <c r="Q64">
-        <v>-3.611672320000002</v>
+        <v>-3.74824768</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.175235472668312</v>
+        <v>0.1787337286863745</v>
       </c>
       <c r="T64">
-        <v>1.417371478202212</v>
+        <v>1.45567881545092</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0750147119533317</v>
+        <v>0.07382400223978675</v>
       </c>
       <c r="W64">
-        <v>0.2181115309214044</v>
+        <v>0.2183923002718583</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3750735597666585</v>
+        <v>0.3691200111989338</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2037186287852293</v>
+        <v>0.2056186287852293</v>
       </c>
       <c r="C65">
-        <v>-19.41318000778645</v>
+        <v>-20.44379356315025</v>
       </c>
       <c r="D65">
-        <v>25.79081999221355</v>
+        <v>25.48420643684975</v>
       </c>
       <c r="E65">
-        <v>26.212</v>
+        <v>26.93600000000001</v>
       </c>
       <c r="F65">
-        <v>45.612</v>
+        <v>46.33600000000001</v>
       </c>
       <c r="G65">
         <v>0.408</v>
@@ -6739,37 +6739,37 @@
         <v>3.97</v>
       </c>
       <c r="M65">
-        <v>10.7553096</v>
+        <v>10.9260288</v>
       </c>
       <c r="N65">
-        <v>-6.785309600000001</v>
+        <v>-6.956028800000001</v>
       </c>
       <c r="O65">
-        <v>-1.35706192</v>
+        <v>-1.39120576</v>
       </c>
       <c r="P65">
-        <v>-5.42824768</v>
+        <v>-5.564823040000001</v>
       </c>
       <c r="Q65">
-        <v>-3.74824768</v>
+        <v>-3.884823040000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1787337286863745</v>
+        <v>0.182426332260996</v>
       </c>
       <c r="T65">
-        <v>1.45567881545092</v>
+        <v>1.496114338102335</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.07382400223978675</v>
+        <v>0.07267050220479009</v>
       </c>
       <c r="W65">
-        <v>0.2183923002718583</v>
+        <v>0.2186642955801105</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3691200111989338</v>
+        <v>0.3633525110239504</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2056186287852293</v>
+        <v>0.2075186287852293</v>
       </c>
       <c r="C66">
-        <v>-20.44379356315025</v>
+        <v>-21.46720243517524</v>
       </c>
       <c r="D66">
-        <v>25.48420643684975</v>
+        <v>25.18479756482476</v>
       </c>
       <c r="E66">
-        <v>26.93600000000001</v>
+        <v>27.66</v>
       </c>
       <c r="F66">
-        <v>46.33600000000001</v>
+        <v>47.06</v>
       </c>
       <c r="G66">
         <v>0.408</v>
@@ -6821,37 +6821,37 @@
         <v>3.97</v>
       </c>
       <c r="M66">
-        <v>10.9260288</v>
+        <v>11.096748</v>
       </c>
       <c r="N66">
-        <v>-6.956028800000001</v>
+        <v>-7.126748000000002</v>
       </c>
       <c r="O66">
-        <v>-1.39120576</v>
+        <v>-1.425349600000001</v>
       </c>
       <c r="P66">
-        <v>-5.564823040000001</v>
+        <v>-5.701398400000001</v>
       </c>
       <c r="Q66">
-        <v>-3.884823040000001</v>
+        <v>-4.021398400000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.182426332260996</v>
+        <v>0.1863299417541674</v>
       </c>
       <c r="T66">
-        <v>1.496114338102335</v>
+        <v>1.538860462048116</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07267050220479009</v>
+        <v>0.07155249447856253</v>
       </c>
       <c r="W66">
-        <v>0.2186642955801105</v>
+        <v>0.218927921801955</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3633525110239504</v>
+        <v>0.3577624723928127</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2075186287852293</v>
+        <v>0.2094186287852293</v>
       </c>
       <c r="C67">
-        <v>-21.46720243517524</v>
+        <v>-22.48365761419999</v>
       </c>
       <c r="D67">
-        <v>25.18479756482476</v>
+        <v>24.89234238580001</v>
       </c>
       <c r="E67">
-        <v>27.66</v>
+        <v>28.38400000000001</v>
       </c>
       <c r="F67">
-        <v>47.06</v>
+        <v>47.78400000000001</v>
       </c>
       <c r="G67">
         <v>0.408</v>
@@ -6903,37 +6903,37 @@
         <v>3.97</v>
       </c>
       <c r="M67">
-        <v>11.096748</v>
+        <v>11.2674672</v>
       </c>
       <c r="N67">
-        <v>-7.126748000000002</v>
+        <v>-7.297467200000002</v>
       </c>
       <c r="O67">
-        <v>-1.425349600000001</v>
+        <v>-1.459493440000001</v>
       </c>
       <c r="P67">
-        <v>-5.701398400000001</v>
+        <v>-5.837973760000002</v>
       </c>
       <c r="Q67">
-        <v>-4.021398400000002</v>
+        <v>-4.157973760000003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1863299417541674</v>
+        <v>0.1904631753351723</v>
       </c>
       <c r="T67">
-        <v>1.538860462048116</v>
+        <v>1.58412106387306</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07155249447856253</v>
+        <v>0.07046836577434189</v>
       </c>
       <c r="W67">
-        <v>0.218927921801955</v>
+        <v>0.2191835593504102</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3577624723928127</v>
+        <v>0.3523418288717094</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2094186287852293</v>
+        <v>0.2113186287852293</v>
       </c>
       <c r="C68">
-        <v>-22.48365761419999</v>
+        <v>-23.49339856601992</v>
       </c>
       <c r="D68">
-        <v>24.89234238580001</v>
+        <v>24.60660143398009</v>
       </c>
       <c r="E68">
-        <v>28.38400000000001</v>
+        <v>29.10800000000001</v>
       </c>
       <c r="F68">
-        <v>47.78400000000001</v>
+        <v>48.50800000000001</v>
       </c>
       <c r="G68">
         <v>0.408</v>
@@ -6985,37 +6985,37 @@
         <v>3.97</v>
       </c>
       <c r="M68">
-        <v>11.2674672</v>
+        <v>11.4381864</v>
       </c>
       <c r="N68">
-        <v>-7.297467200000002</v>
+        <v>-7.468186400000003</v>
       </c>
       <c r="O68">
-        <v>-1.459493440000001</v>
+        <v>-1.493637280000001</v>
       </c>
       <c r="P68">
-        <v>-5.837973760000002</v>
+        <v>-5.974549120000002</v>
       </c>
       <c r="Q68">
-        <v>-4.157973760000003</v>
+        <v>-4.294549120000003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1904631753351723</v>
+        <v>0.1948469079210866</v>
       </c>
       <c r="T68">
-        <v>1.58412106387306</v>
+        <v>1.632124732475274</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07046836577434189</v>
+        <v>0.0694165991209935</v>
       </c>
       <c r="W68">
-        <v>0.2191835593504102</v>
+        <v>0.2194315659272697</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3523418288717094</v>
+        <v>0.3470829956049675</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2113186287852293</v>
+        <v>0.2132186287852293</v>
       </c>
       <c r="C69">
-        <v>-23.49339856601992</v>
+        <v>-24.49665388583584</v>
       </c>
       <c r="D69">
-        <v>24.60660143398009</v>
+        <v>24.32734611416417</v>
       </c>
       <c r="E69">
-        <v>29.10800000000001</v>
+        <v>29.83200000000001</v>
       </c>
       <c r="F69">
-        <v>48.50800000000001</v>
+        <v>49.23200000000001</v>
       </c>
       <c r="G69">
         <v>0.408</v>
@@ -7067,37 +7067,37 @@
         <v>3.97</v>
       </c>
       <c r="M69">
-        <v>11.4381864</v>
+        <v>11.6089056</v>
       </c>
       <c r="N69">
-        <v>-7.468186400000003</v>
+        <v>-7.638905600000002</v>
       </c>
       <c r="O69">
-        <v>-1.493637280000001</v>
+        <v>-1.52778112</v>
       </c>
       <c r="P69">
-        <v>-5.974549120000002</v>
+        <v>-6.111124480000002</v>
       </c>
       <c r="Q69">
-        <v>-4.294549120000003</v>
+        <v>-4.431124480000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1948469079210866</v>
+        <v>0.1995046237936206</v>
       </c>
       <c r="T69">
-        <v>1.632124732475274</v>
+        <v>1.683128630365126</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0694165991209935</v>
+        <v>0.0683957667809789</v>
       </c>
       <c r="W69">
-        <v>0.2194315659272697</v>
+        <v>0.2196722781930452</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3470829956049675</v>
+        <v>0.3419788339048945</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2132186287852293</v>
+        <v>0.2151186287852293</v>
       </c>
       <c r="C70">
-        <v>-24.49665388583584</v>
+        <v>-25.49364190817295</v>
       </c>
       <c r="D70">
-        <v>24.32734611416417</v>
+        <v>24.05435809182705</v>
       </c>
       <c r="E70">
-        <v>29.83200000000001</v>
+        <v>30.55600000000001</v>
       </c>
       <c r="F70">
-        <v>49.23200000000001</v>
+        <v>49.95600000000001</v>
       </c>
       <c r="G70">
         <v>0.408</v>
@@ -7149,37 +7149,37 @@
         <v>3.97</v>
       </c>
       <c r="M70">
-        <v>11.6089056</v>
+        <v>11.7796248</v>
       </c>
       <c r="N70">
-        <v>-7.638905600000002</v>
+        <v>-7.809624800000003</v>
       </c>
       <c r="O70">
-        <v>-1.52778112</v>
+        <v>-1.561924960000001</v>
       </c>
       <c r="P70">
-        <v>-6.111124480000002</v>
+        <v>-6.247699840000002</v>
       </c>
       <c r="Q70">
-        <v>-4.431124480000002</v>
+        <v>-4.567699840000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1995046237936206</v>
+        <v>0.2044628374643825</v>
       </c>
       <c r="T70">
-        <v>1.683128630365126</v>
+        <v>1.737423102312389</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0683957667809789</v>
+        <v>0.06740452378415311</v>
       </c>
       <c r="W70">
-        <v>0.2196722781930452</v>
+        <v>0.2199060132916967</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3419788339048945</v>
+        <v>0.3370226189207656</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2151186287852293</v>
+        <v>0.2170186287852293</v>
       </c>
       <c r="C71">
-        <v>-25.49364190817295</v>
+        <v>-26.48457127619049</v>
       </c>
       <c r="D71">
-        <v>24.05435809182705</v>
+        <v>23.78742872380951</v>
       </c>
       <c r="E71">
-        <v>30.55600000000001</v>
+        <v>31.28000000000001</v>
       </c>
       <c r="F71">
-        <v>49.95600000000001</v>
+        <v>50.68000000000001</v>
       </c>
       <c r="G71">
         <v>0.408</v>
@@ -7231,37 +7231,37 @@
         <v>3.97</v>
       </c>
       <c r="M71">
-        <v>11.7796248</v>
+        <v>11.950344</v>
       </c>
       <c r="N71">
-        <v>-7.809624800000003</v>
+        <v>-7.980344000000003</v>
       </c>
       <c r="O71">
-        <v>-1.561924960000001</v>
+        <v>-1.596068800000001</v>
       </c>
       <c r="P71">
-        <v>-6.247699840000002</v>
+        <v>-6.384275200000003</v>
       </c>
       <c r="Q71">
-        <v>-4.567699840000002</v>
+        <v>-4.704275200000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2044628374643825</v>
+        <v>0.2097515987131953</v>
       </c>
       <c r="T71">
-        <v>1.737423102312389</v>
+        <v>1.795337205722802</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06740452378415311</v>
+        <v>0.06644160201580805</v>
       </c>
       <c r="W71">
-        <v>0.2199060132916967</v>
+        <v>0.2201330702446725</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3370226189207656</v>
+        <v>0.3322080100790403</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2170186287852293</v>
+        <v>0.2189186287852293</v>
       </c>
       <c r="C72">
-        <v>-26.48457127619049</v>
+        <v>-27.4696414735019</v>
       </c>
       <c r="D72">
-        <v>23.78742872380951</v>
+        <v>23.52635852649811</v>
       </c>
       <c r="E72">
-        <v>31.28000000000001</v>
+        <v>32.00400000000001</v>
       </c>
       <c r="F72">
-        <v>50.68000000000001</v>
+        <v>51.40400000000001</v>
       </c>
       <c r="G72">
         <v>0.408</v>
@@ -7313,37 +7313,37 @@
         <v>3.97</v>
       </c>
       <c r="M72">
-        <v>11.950344</v>
+        <v>12.1210632</v>
       </c>
       <c r="N72">
-        <v>-7.980344000000003</v>
+        <v>-8.151063200000003</v>
       </c>
       <c r="O72">
-        <v>-1.596068800000001</v>
+        <v>-1.630212640000001</v>
       </c>
       <c r="P72">
-        <v>-6.384275200000003</v>
+        <v>-6.520850560000002</v>
       </c>
       <c r="Q72">
-        <v>-4.704275200000003</v>
+        <v>-4.840850560000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2097515987131953</v>
+        <v>0.2154051021170986</v>
       </c>
       <c r="T72">
-        <v>1.795337205722802</v>
+        <v>1.857245385230485</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06644160201580805</v>
+        <v>0.06550580480431781</v>
       </c>
       <c r="W72">
-        <v>0.2201330702446725</v>
+        <v>0.2203537312271419</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3322080100790403</v>
+        <v>0.3275290240215891</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2189186287852293</v>
+        <v>0.2208186287852293</v>
       </c>
       <c r="C73">
-        <v>-27.46964147350189</v>
+        <v>-28.44904332135431</v>
       </c>
       <c r="D73">
-        <v>23.52635852649811</v>
+        <v>23.27095667864569</v>
       </c>
       <c r="E73">
-        <v>32.004</v>
+        <v>32.728</v>
       </c>
       <c r="F73">
-        <v>51.404</v>
+        <v>52.128</v>
       </c>
       <c r="G73">
         <v>0.408</v>
@@ -7395,37 +7395,37 @@
         <v>3.97</v>
       </c>
       <c r="M73">
-        <v>12.1210632</v>
+        <v>12.2917824</v>
       </c>
       <c r="N73">
-        <v>-8.151063200000003</v>
+        <v>-8.3217824</v>
       </c>
       <c r="O73">
-        <v>-1.630212640000001</v>
+        <v>-1.66435648</v>
       </c>
       <c r="P73">
-        <v>-6.520850560000002</v>
+        <v>-6.65742592</v>
       </c>
       <c r="Q73">
-        <v>-4.840850560000002</v>
+        <v>-4.97742592</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2154051021170985</v>
+        <v>0.2214624271927091</v>
       </c>
       <c r="T73">
-        <v>1.857245385230484</v>
+        <v>1.923575577560144</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06550580480431782</v>
+        <v>0.06459600195981341</v>
       </c>
       <c r="W73">
-        <v>0.2203537312271419</v>
+        <v>0.220568262737876</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.327529024021589</v>
+        <v>0.322980009799067</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2208186287852293</v>
+        <v>0.2227186287852293</v>
       </c>
       <c r="C74">
-        <v>-28.44904332135431</v>
+        <v>-29.42295944377182</v>
       </c>
       <c r="D74">
-        <v>23.27095667864569</v>
+        <v>23.02104055622818</v>
       </c>
       <c r="E74">
-        <v>32.728</v>
+        <v>33.45200000000001</v>
       </c>
       <c r="F74">
-        <v>52.128</v>
+        <v>52.852</v>
       </c>
       <c r="G74">
         <v>0.408</v>
@@ -7477,37 +7477,37 @@
         <v>3.97</v>
       </c>
       <c r="M74">
-        <v>12.2917824</v>
+        <v>12.4625016</v>
       </c>
       <c r="N74">
-        <v>-8.3217824</v>
+        <v>-8.492501600000001</v>
       </c>
       <c r="O74">
-        <v>-1.66435648</v>
+        <v>-1.69850032</v>
       </c>
       <c r="P74">
-        <v>-6.65742592</v>
+        <v>-6.794001280000001</v>
       </c>
       <c r="Q74">
-        <v>-4.97742592</v>
+        <v>-5.114001280000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2214624271927091</v>
+        <v>0.2279684430146613</v>
       </c>
       <c r="T74">
-        <v>1.923575577560144</v>
+        <v>1.994819117469779</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06459600195981341</v>
+        <v>0.06371112522063788</v>
       </c>
       <c r="W74">
-        <v>0.220568262737876</v>
+        <v>0.2207769166729736</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.322980009799067</v>
+        <v>0.3185556261031894</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2227186287852293</v>
+        <v>0.2246186287852293</v>
       </c>
       <c r="C75">
-        <v>-29.42295944377182</v>
+        <v>-30.3915647030447</v>
       </c>
       <c r="D75">
-        <v>23.02104055622818</v>
+        <v>22.7764352969553</v>
       </c>
       <c r="E75">
-        <v>33.45200000000001</v>
+        <v>34.176</v>
       </c>
       <c r="F75">
-        <v>52.852</v>
+        <v>53.576</v>
       </c>
       <c r="G75">
         <v>0.408</v>
@@ -7559,37 +7559,37 @@
         <v>3.97</v>
       </c>
       <c r="M75">
-        <v>12.4625016</v>
+        <v>12.6332208</v>
       </c>
       <c r="N75">
-        <v>-8.492501600000001</v>
+        <v>-8.663220800000001</v>
       </c>
       <c r="O75">
-        <v>-1.69850032</v>
+        <v>-1.73264416</v>
       </c>
       <c r="P75">
-        <v>-6.794001280000001</v>
+        <v>-6.930576640000001</v>
       </c>
       <c r="Q75">
-        <v>-5.114001280000001</v>
+        <v>-5.250576640000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2279684430146613</v>
+        <v>0.2349749215921483</v>
       </c>
       <c r="T75">
-        <v>1.994819117469779</v>
+        <v>2.071542929680155</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06371112522063788</v>
+        <v>0.06285016406900765</v>
       </c>
       <c r="W75">
-        <v>0.2207769166729736</v>
+        <v>0.220979931312528</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3185556261031894</v>
+        <v>0.3142508203450382</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2246186287852293</v>
+        <v>0.2265186287852293</v>
       </c>
       <c r="C76">
-        <v>-30.3915647030447</v>
+        <v>-31.35502660774766</v>
       </c>
       <c r="D76">
-        <v>22.7764352969553</v>
+        <v>22.53697339225234</v>
       </c>
       <c r="E76">
-        <v>34.176</v>
+        <v>34.90000000000001</v>
       </c>
       <c r="F76">
-        <v>53.576</v>
+        <v>54.3</v>
       </c>
       <c r="G76">
         <v>0.408</v>
@@ -7641,37 +7641,37 @@
         <v>3.97</v>
       </c>
       <c r="M76">
-        <v>12.6332208</v>
+        <v>12.80394</v>
       </c>
       <c r="N76">
-        <v>-8.663220800000001</v>
+        <v>-8.833940000000002</v>
       </c>
       <c r="O76">
-        <v>-1.73264416</v>
+        <v>-1.766788</v>
       </c>
       <c r="P76">
-        <v>-6.930576640000001</v>
+        <v>-7.067152000000002</v>
       </c>
       <c r="Q76">
-        <v>-5.250576640000001</v>
+        <v>-5.387152000000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2349749215921483</v>
+        <v>0.2425419184558343</v>
       </c>
       <c r="T76">
-        <v>2.071542929680155</v>
+        <v>2.154404646867361</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06285016406900765</v>
+        <v>0.06201216188142087</v>
       </c>
       <c r="W76">
-        <v>0.220979931312528</v>
+        <v>0.221177532228361</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3142508203450382</v>
+        <v>0.3100608094071042</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2265186287852293</v>
+        <v>0.2284186287852293</v>
       </c>
       <c r="C77">
-        <v>-31.35502660774766</v>
+        <v>-32.31350569528719</v>
       </c>
       <c r="D77">
-        <v>22.53697339225234</v>
+        <v>22.30249430471282</v>
       </c>
       <c r="E77">
-        <v>34.90000000000001</v>
+        <v>35.62400000000001</v>
       </c>
       <c r="F77">
-        <v>54.3</v>
+        <v>55.02400000000001</v>
       </c>
       <c r="G77">
         <v>0.408</v>
@@ -7723,37 +7723,37 @@
         <v>3.97</v>
       </c>
       <c r="M77">
-        <v>12.80394</v>
+        <v>12.9746592</v>
       </c>
       <c r="N77">
-        <v>-8.833940000000002</v>
+        <v>-9.004659200000003</v>
       </c>
       <c r="O77">
-        <v>-1.766788</v>
+        <v>-1.800931840000001</v>
       </c>
       <c r="P77">
-        <v>-7.067152000000002</v>
+        <v>-7.203727360000002</v>
       </c>
       <c r="Q77">
-        <v>-5.387152000000002</v>
+        <v>-5.523727360000002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2425419184558343</v>
+        <v>0.250739498391494</v>
       </c>
       <c r="T77">
-        <v>2.154404646867361</v>
+        <v>2.244171507153502</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06201216188142087</v>
+        <v>0.06119621238298111</v>
       </c>
       <c r="W77">
-        <v>0.221177532228361</v>
+        <v>0.2213699331200931</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3100608094071042</v>
+        <v>0.3059810619149056</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2284186287852293</v>
+        <v>0.2303186287852293</v>
       </c>
       <c r="C78">
-        <v>-32.31350569528719</v>
+        <v>-33.26715589081447</v>
       </c>
       <c r="D78">
-        <v>22.30249430471282</v>
+        <v>22.07284410918553</v>
       </c>
       <c r="E78">
-        <v>35.62400000000001</v>
+        <v>36.34800000000001</v>
       </c>
       <c r="F78">
-        <v>55.02400000000001</v>
+        <v>55.748</v>
       </c>
       <c r="G78">
         <v>0.408</v>
@@ -7805,37 +7805,37 @@
         <v>3.97</v>
       </c>
       <c r="M78">
-        <v>12.9746592</v>
+        <v>13.1453784</v>
       </c>
       <c r="N78">
-        <v>-9.004659200000003</v>
+        <v>-9.175378400000003</v>
       </c>
       <c r="O78">
-        <v>-1.800931840000001</v>
+        <v>-1.835075680000001</v>
       </c>
       <c r="P78">
-        <v>-7.203727360000002</v>
+        <v>-7.340302720000002</v>
       </c>
       <c r="Q78">
-        <v>-5.523727360000002</v>
+        <v>-5.660302720000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.250739498391494</v>
+        <v>0.2596499113650372</v>
       </c>
       <c r="T78">
-        <v>2.244171507153502</v>
+        <v>2.341744181377567</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06119621238298111</v>
+        <v>0.06040145637800734</v>
       </c>
       <c r="W78">
-        <v>0.2213699331200931</v>
+        <v>0.2215573365860659</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3059810619149056</v>
+        <v>0.3020072818900366</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2303186287852293</v>
+        <v>0.2322186287852293</v>
       </c>
       <c r="C79">
-        <v>-33.26715589081447</v>
+        <v>-34.21612484418966</v>
       </c>
       <c r="D79">
-        <v>22.07284410918553</v>
+        <v>21.84787515581035</v>
       </c>
       <c r="E79">
-        <v>36.34800000000001</v>
+        <v>37.07200000000001</v>
       </c>
       <c r="F79">
-        <v>55.748</v>
+        <v>56.47200000000001</v>
       </c>
       <c r="G79">
         <v>0.408</v>
@@ -7887,37 +7887,37 @@
         <v>3.97</v>
       </c>
       <c r="M79">
-        <v>13.1453784</v>
+        <v>13.3160976</v>
       </c>
       <c r="N79">
-        <v>-9.175378400000003</v>
+        <v>-9.346097600000004</v>
       </c>
       <c r="O79">
-        <v>-1.835075680000001</v>
+        <v>-1.869219520000001</v>
       </c>
       <c r="P79">
-        <v>-7.340302720000002</v>
+        <v>-7.476878080000003</v>
       </c>
       <c r="Q79">
-        <v>-5.660302720000002</v>
+        <v>-5.796878080000003</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2596499113650372</v>
+        <v>0.2693703618816298</v>
       </c>
       <c r="T79">
-        <v>2.341744181377567</v>
+        <v>2.448187098712911</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06040145637800734</v>
+        <v>0.05962707873213544</v>
       </c>
       <c r="W79">
-        <v>0.2215573365860659</v>
+        <v>0.2217399348349625</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3020072818900366</v>
+        <v>0.2981353936606771</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2322186287852293</v>
+        <v>0.2341186287852293</v>
       </c>
       <c r="C80">
-        <v>-34.21612484418966</v>
+        <v>-35.16055424654783</v>
       </c>
       <c r="D80">
-        <v>21.84787515581035</v>
+        <v>21.62744575345217</v>
       </c>
       <c r="E80">
-        <v>37.07200000000001</v>
+        <v>37.79600000000001</v>
       </c>
       <c r="F80">
-        <v>56.47200000000001</v>
+        <v>57.19600000000001</v>
       </c>
       <c r="G80">
         <v>0.408</v>
@@ -7969,37 +7969,37 @@
         <v>3.97</v>
       </c>
       <c r="M80">
-        <v>13.3160976</v>
+        <v>13.4868168</v>
       </c>
       <c r="N80">
-        <v>-9.346097600000004</v>
+        <v>-9.516816800000001</v>
       </c>
       <c r="O80">
-        <v>-1.869219520000001</v>
+        <v>-1.90336336</v>
       </c>
       <c r="P80">
-        <v>-7.476878080000003</v>
+        <v>-7.613453440000001</v>
       </c>
       <c r="Q80">
-        <v>-5.796878080000003</v>
+        <v>-5.933453440000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2693703618816298</v>
+        <v>0.2800165695902789</v>
       </c>
       <c r="T80">
-        <v>2.448187098712911</v>
+        <v>2.564767436746859</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05962707873213544</v>
+        <v>0.05887230558362741</v>
       </c>
       <c r="W80">
-        <v>0.2217399348349625</v>
+        <v>0.2219179103433807</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2981353936606771</v>
+        <v>0.2943615279181371</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2341186287852293</v>
+        <v>0.2360186287852293</v>
       </c>
       <c r="C81">
-        <v>-35.16055424654783</v>
+        <v>-36.1005801278928</v>
       </c>
       <c r="D81">
-        <v>21.62744575345217</v>
+        <v>21.4114198721072</v>
       </c>
       <c r="E81">
-        <v>37.79600000000001</v>
+        <v>38.52000000000001</v>
       </c>
       <c r="F81">
-        <v>57.19600000000001</v>
+        <v>57.92000000000001</v>
       </c>
       <c r="G81">
         <v>0.408</v>
@@ -8051,37 +8051,37 @@
         <v>3.97</v>
       </c>
       <c r="M81">
-        <v>13.4868168</v>
+        <v>13.657536</v>
       </c>
       <c r="N81">
-        <v>-9.516816800000001</v>
+        <v>-9.687536000000001</v>
       </c>
       <c r="O81">
-        <v>-1.90336336</v>
+        <v>-1.9375072</v>
       </c>
       <c r="P81">
-        <v>-7.613453440000001</v>
+        <v>-7.750028800000001</v>
       </c>
       <c r="Q81">
-        <v>-5.933453440000001</v>
+        <v>-6.070028800000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2800165695902789</v>
+        <v>0.2917273980697929</v>
       </c>
       <c r="T81">
-        <v>2.564767436746859</v>
+        <v>2.693005808584203</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05887230558362741</v>
+        <v>0.05813640176383206</v>
       </c>
       <c r="W81">
-        <v>0.2219179103433807</v>
+        <v>0.2220914364640884</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2943615279181371</v>
+        <v>0.2906820088191604</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2360186287852293</v>
+        <v>0.2379186287852293</v>
       </c>
       <c r="C82">
-        <v>-36.1005801278928</v>
+        <v>-37.03633313703219</v>
       </c>
       <c r="D82">
-        <v>21.4114198721072</v>
+        <v>21.19966686296782</v>
       </c>
       <c r="E82">
-        <v>38.52000000000001</v>
+        <v>39.24400000000001</v>
       </c>
       <c r="F82">
-        <v>57.92000000000001</v>
+        <v>58.64400000000001</v>
       </c>
       <c r="G82">
         <v>0.408</v>
@@ -8133,37 +8133,37 @@
         <v>3.97</v>
       </c>
       <c r="M82">
-        <v>13.657536</v>
+        <v>13.8282552</v>
       </c>
       <c r="N82">
-        <v>-9.687536000000001</v>
+        <v>-9.858255200000002</v>
       </c>
       <c r="O82">
-        <v>-1.9375072</v>
+        <v>-1.97165104</v>
       </c>
       <c r="P82">
-        <v>-7.750028800000001</v>
+        <v>-7.886604160000002</v>
       </c>
       <c r="Q82">
-        <v>-6.070028800000001</v>
+        <v>-6.206604160000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2917273980697929</v>
+        <v>0.3046709453366241</v>
       </c>
       <c r="T82">
-        <v>2.693005808584203</v>
+        <v>2.834742956404424</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05813640176383206</v>
+        <v>0.05741866840872303</v>
       </c>
       <c r="W82">
-        <v>0.2220914364640884</v>
+        <v>0.2222606779892231</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2906820088191604</v>
+        <v>0.287093342043615</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2379186287852293</v>
+        <v>0.2398186287852293</v>
       </c>
       <c r="C83">
-        <v>-37.03633313703219</v>
+        <v>-37.96793880506433</v>
       </c>
       <c r="D83">
-        <v>21.19966686296782</v>
+        <v>20.99206119493568</v>
       </c>
       <c r="E83">
-        <v>39.24400000000001</v>
+        <v>39.96800000000001</v>
       </c>
       <c r="F83">
-        <v>58.64400000000001</v>
+        <v>59.36800000000001</v>
       </c>
       <c r="G83">
         <v>0.408</v>
@@ -8215,37 +8215,37 @@
         <v>3.97</v>
       </c>
       <c r="M83">
-        <v>13.8282552</v>
+        <v>13.9989744</v>
       </c>
       <c r="N83">
-        <v>-9.858255200000002</v>
+        <v>-10.0289744</v>
       </c>
       <c r="O83">
-        <v>-1.97165104</v>
+        <v>-2.005794880000001</v>
       </c>
       <c r="P83">
-        <v>-7.886604160000002</v>
+        <v>-8.023179520000003</v>
       </c>
       <c r="Q83">
-        <v>-6.206604160000002</v>
+        <v>-6.343179520000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3046709453366241</v>
+        <v>0.3190526645219921</v>
       </c>
       <c r="T83">
-        <v>2.834742956404424</v>
+        <v>2.992228676204669</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05741866840872303</v>
+        <v>0.05671844074520201</v>
       </c>
       <c r="W83">
-        <v>0.2222606779892231</v>
+        <v>0.2224257916722814</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.287093342043615</v>
+        <v>0.2835922037260101</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2398186287852293</v>
+        <v>0.2417186287852293</v>
       </c>
       <c r="C84">
-        <v>-37.96793880506433</v>
+        <v>-38.89551779353359</v>
       </c>
       <c r="D84">
-        <v>20.99206119493568</v>
+        <v>20.78848220646643</v>
       </c>
       <c r="E84">
-        <v>39.96800000000001</v>
+        <v>40.69200000000001</v>
       </c>
       <c r="F84">
-        <v>59.36800000000001</v>
+        <v>60.09200000000001</v>
       </c>
       <c r="G84">
         <v>0.408</v>
@@ -8297,37 +8297,37 @@
         <v>3.97</v>
       </c>
       <c r="M84">
-        <v>13.9989744</v>
+        <v>14.1696936</v>
       </c>
       <c r="N84">
-        <v>-10.0289744</v>
+        <v>-10.1996936</v>
       </c>
       <c r="O84">
-        <v>-2.005794880000001</v>
+        <v>-2.039938720000001</v>
       </c>
       <c r="P84">
-        <v>-8.023179520000003</v>
+        <v>-8.159754880000003</v>
       </c>
       <c r="Q84">
-        <v>-6.343179520000003</v>
+        <v>-6.479754880000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3190526645219921</v>
+        <v>0.3351263506703446</v>
       </c>
       <c r="T84">
-        <v>2.992228676204669</v>
+        <v>3.168242127746121</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05671844074520201</v>
+        <v>0.05603508603742849</v>
       </c>
       <c r="W84">
-        <v>0.2224257916722814</v>
+        <v>0.2225869267123744</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2835922037260101</v>
+        <v>0.2801754301871425</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2417186287852293</v>
+        <v>0.2436186287852293</v>
       </c>
       <c r="C85">
-        <v>-38.89551779353359</v>
+        <v>-39.81918612828465</v>
       </c>
       <c r="D85">
-        <v>20.78848220646643</v>
+        <v>20.58881387171536</v>
       </c>
       <c r="E85">
-        <v>40.69200000000001</v>
+        <v>41.41600000000001</v>
       </c>
       <c r="F85">
-        <v>60.09200000000001</v>
+        <v>60.81600000000001</v>
       </c>
       <c r="G85">
         <v>0.408</v>
@@ -8379,37 +8379,37 @@
         <v>3.97</v>
       </c>
       <c r="M85">
-        <v>14.1696936</v>
+        <v>14.3404128</v>
       </c>
       <c r="N85">
-        <v>-10.1996936</v>
+        <v>-10.3704128</v>
       </c>
       <c r="O85">
-        <v>-2.039938720000001</v>
+        <v>-2.074082560000001</v>
       </c>
       <c r="P85">
-        <v>-8.159754880000003</v>
+        <v>-8.296330240000003</v>
       </c>
       <c r="Q85">
-        <v>-6.479754880000003</v>
+        <v>-6.616330240000003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3351263506703446</v>
+        <v>0.3532092475872413</v>
       </c>
       <c r="T85">
-        <v>3.168242127746121</v>
+        <v>3.366257260730254</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05603508603742849</v>
+        <v>0.05536800167984005</v>
       </c>
       <c r="W85">
-        <v>0.2225869267123744</v>
+        <v>0.2227442252038937</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2801754301871425</v>
+        <v>0.2768400083992002</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2436186287852293</v>
+        <v>0.2455186287852293</v>
       </c>
       <c r="C86">
-        <v>-39.81918612828463</v>
+        <v>-40.73905541996862</v>
       </c>
       <c r="D86">
-        <v>20.58881387171537</v>
+        <v>20.39294458003138</v>
       </c>
       <c r="E86">
-        <v>41.416</v>
+        <v>42.14000000000001</v>
       </c>
       <c r="F86">
-        <v>60.816</v>
+        <v>61.54000000000001</v>
       </c>
       <c r="G86">
         <v>0.408</v>
@@ -8461,37 +8461,37 @@
         <v>3.97</v>
       </c>
       <c r="M86">
-        <v>14.3404128</v>
+        <v>14.511132</v>
       </c>
       <c r="N86">
-        <v>-10.3704128</v>
+        <v>-10.541132</v>
       </c>
       <c r="O86">
-        <v>-2.07408256</v>
+        <v>-2.1082264</v>
       </c>
       <c r="P86">
-        <v>-8.29633024</v>
+        <v>-8.432905600000002</v>
       </c>
       <c r="Q86">
-        <v>-6.61633024</v>
+        <v>-6.752905600000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.353209247587241</v>
+        <v>0.3737031974263905</v>
       </c>
       <c r="T86">
-        <v>3.366257260730252</v>
+        <v>3.590674411445602</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05536800167984007</v>
+        <v>0.05471661342478312</v>
       </c>
       <c r="W86">
-        <v>0.2227442252038937</v>
+        <v>0.2228978225544362</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2768400083992003</v>
+        <v>0.2735830671239157</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2455186287852293</v>
+        <v>0.2474186287852293</v>
       </c>
       <c r="C87">
-        <v>-40.73905541996862</v>
+        <v>-41.65523307208099</v>
       </c>
       <c r="D87">
-        <v>20.39294458003138</v>
+        <v>20.20076692791901</v>
       </c>
       <c r="E87">
-        <v>42.14000000000001</v>
+        <v>42.864</v>
       </c>
       <c r="F87">
-        <v>61.54000000000001</v>
+        <v>62.264</v>
       </c>
       <c r="G87">
         <v>0.408</v>
@@ -8543,37 +8543,37 @@
         <v>3.97</v>
       </c>
       <c r="M87">
-        <v>14.511132</v>
+        <v>14.6818512</v>
       </c>
       <c r="N87">
-        <v>-10.541132</v>
+        <v>-10.7118512</v>
       </c>
       <c r="O87">
-        <v>-2.1082264</v>
+        <v>-2.14237024</v>
       </c>
       <c r="P87">
-        <v>-8.432905600000002</v>
+        <v>-8.569480960000002</v>
       </c>
       <c r="Q87">
-        <v>-6.752905600000002</v>
+        <v>-6.889480960000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3737031974263905</v>
+        <v>0.3971248543854183</v>
       </c>
       <c r="T87">
-        <v>3.590674411445602</v>
+        <v>3.847151155120288</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05471661342478312</v>
+        <v>0.05408037373379727</v>
       </c>
       <c r="W87">
-        <v>0.2228978225544362</v>
+        <v>0.2230478478735706</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2735830671239157</v>
+        <v>0.2704018686689863</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2474186287852293</v>
+        <v>0.2493186287852293</v>
       </c>
       <c r="C88">
-        <v>-41.65523307208099</v>
+        <v>-42.56782247734644</v>
       </c>
       <c r="D88">
-        <v>20.20076692791901</v>
+        <v>20.01217752265357</v>
       </c>
       <c r="E88">
-        <v>42.864</v>
+        <v>43.58800000000001</v>
       </c>
       <c r="F88">
-        <v>62.264</v>
+        <v>62.98800000000001</v>
       </c>
       <c r="G88">
         <v>0.408</v>
@@ -8625,37 +8625,37 @@
         <v>3.97</v>
       </c>
       <c r="M88">
-        <v>14.6818512</v>
+        <v>14.8525704</v>
       </c>
       <c r="N88">
-        <v>-10.7118512</v>
+        <v>-10.8825704</v>
       </c>
       <c r="O88">
-        <v>-2.14237024</v>
+        <v>-2.17651408</v>
       </c>
       <c r="P88">
-        <v>-8.569480960000002</v>
+        <v>-8.706056320000002</v>
       </c>
       <c r="Q88">
-        <v>-6.889480960000002</v>
+        <v>-7.026056320000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3971248543854183</v>
+        <v>0.4241498431842967</v>
       </c>
       <c r="T88">
-        <v>3.847151155120288</v>
+        <v>4.14308585936031</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05408037373379727</v>
+        <v>0.05345876024260419</v>
       </c>
       <c r="W88">
-        <v>0.2230478478735706</v>
+        <v>0.2231944243347939</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2704018686689863</v>
+        <v>0.267293801213021</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2493186287852293</v>
+        <v>0.2512186287852293</v>
       </c>
       <c r="C89">
-        <v>-42.56782247734644</v>
+        <v>-43.47692320320512</v>
       </c>
       <c r="D89">
-        <v>20.01217752265357</v>
+        <v>19.82707679679488</v>
       </c>
       <c r="E89">
-        <v>43.58800000000001</v>
+        <v>44.312</v>
       </c>
       <c r="F89">
-        <v>62.98800000000001</v>
+        <v>63.712</v>
       </c>
       <c r="G89">
         <v>0.408</v>
@@ -8707,37 +8707,37 @@
         <v>3.97</v>
       </c>
       <c r="M89">
-        <v>14.8525704</v>
+        <v>15.0232896</v>
       </c>
       <c r="N89">
-        <v>-10.8825704</v>
+        <v>-11.0532896</v>
       </c>
       <c r="O89">
-        <v>-2.17651408</v>
+        <v>-2.21065792</v>
       </c>
       <c r="P89">
-        <v>-8.706056320000002</v>
+        <v>-8.842631680000002</v>
       </c>
       <c r="Q89">
-        <v>-7.026056320000002</v>
+        <v>-7.162631680000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4241498431842967</v>
+        <v>0.4556789967829881</v>
       </c>
       <c r="T89">
-        <v>4.14308585936031</v>
+        <v>4.488343014307003</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05345876024260419</v>
+        <v>0.05285127433075642</v>
       </c>
       <c r="W89">
-        <v>0.2231944243347939</v>
+        <v>0.2233376695128076</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.267293801213021</v>
+        <v>0.264256371653782</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2512186287852293</v>
+        <v>0.2531186287852293</v>
       </c>
       <c r="C90">
-        <v>-43.47692320320512</v>
+        <v>-44.38263116709937</v>
       </c>
       <c r="D90">
-        <v>19.82707679679488</v>
+        <v>19.64536883290064</v>
       </c>
       <c r="E90">
-        <v>44.312</v>
+        <v>45.03600000000001</v>
       </c>
       <c r="F90">
-        <v>63.712</v>
+        <v>64.43600000000001</v>
       </c>
       <c r="G90">
         <v>0.408</v>
@@ -8789,37 +8789,37 @@
         <v>3.97</v>
       </c>
       <c r="M90">
-        <v>15.0232896</v>
+        <v>15.1940088</v>
       </c>
       <c r="N90">
-        <v>-11.0532896</v>
+        <v>-11.2240088</v>
       </c>
       <c r="O90">
-        <v>-2.21065792</v>
+        <v>-2.244801760000001</v>
       </c>
       <c r="P90">
-        <v>-8.842631680000002</v>
+        <v>-8.979207040000002</v>
       </c>
       <c r="Q90">
-        <v>-7.162631680000002</v>
+        <v>-7.299207040000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4556789967829881</v>
+        <v>0.4929407237632597</v>
       </c>
       <c r="T90">
-        <v>4.488343014307003</v>
+        <v>4.896374197425821</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05285127433075642</v>
+        <v>0.05225743978771422</v>
       </c>
       <c r="W90">
-        <v>0.2233376695128076</v>
+        <v>0.223477695698057</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.264256371653782</v>
+        <v>0.261287198938571</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2531186287852293</v>
+        <v>0.2550186287852293</v>
       </c>
       <c r="C91">
-        <v>-44.38263116709937</v>
+        <v>-45.28503880220929</v>
       </c>
       <c r="D91">
-        <v>19.64536883290064</v>
+        <v>19.46696119779072</v>
       </c>
       <c r="E91">
-        <v>45.03600000000001</v>
+        <v>45.76000000000001</v>
       </c>
       <c r="F91">
-        <v>64.43600000000001</v>
+        <v>65.16000000000001</v>
       </c>
       <c r="G91">
         <v>0.408</v>
@@ -8871,37 +8871,37 @@
         <v>3.97</v>
       </c>
       <c r="M91">
-        <v>15.1940088</v>
+        <v>15.364728</v>
       </c>
       <c r="N91">
-        <v>-11.2240088</v>
+        <v>-11.394728</v>
       </c>
       <c r="O91">
-        <v>-2.244801760000001</v>
+        <v>-2.278945600000001</v>
       </c>
       <c r="P91">
-        <v>-8.979207040000002</v>
+        <v>-9.115782400000004</v>
       </c>
       <c r="Q91">
-        <v>-7.299207040000002</v>
+        <v>-7.435782400000004</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4929407237632597</v>
+        <v>0.5376547961395858</v>
       </c>
       <c r="T91">
-        <v>4.896374197425821</v>
+        <v>5.386011617168405</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05225743978771422</v>
+        <v>0.05167680156785072</v>
       </c>
       <c r="W91">
-        <v>0.223477695698057</v>
+        <v>0.2236146101903008</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.261287198938571</v>
+        <v>0.2583840078392535</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2550186287852293</v>
+        <v>0.2569186287852293</v>
       </c>
       <c r="C92">
-        <v>-45.28503880220929</v>
+        <v>-46.18423521423897</v>
       </c>
       <c r="D92">
-        <v>19.46696119779072</v>
+        <v>19.29176478576103</v>
       </c>
       <c r="E92">
-        <v>45.76000000000001</v>
+        <v>46.484</v>
       </c>
       <c r="F92">
-        <v>65.16000000000001</v>
+        <v>65.884</v>
       </c>
       <c r="G92">
         <v>0.408</v>
@@ -8953,37 +8953,37 @@
         <v>3.97</v>
       </c>
       <c r="M92">
-        <v>15.364728</v>
+        <v>15.5354472</v>
       </c>
       <c r="N92">
-        <v>-11.394728</v>
+        <v>-11.5654472</v>
       </c>
       <c r="O92">
-        <v>-2.278945600000001</v>
+        <v>-2.31308944</v>
       </c>
       <c r="P92">
-        <v>-9.115782400000004</v>
+        <v>-9.252357760000001</v>
       </c>
       <c r="Q92">
-        <v>-7.435782400000004</v>
+        <v>-7.572357760000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5376547961395858</v>
+        <v>0.5923053290439841</v>
       </c>
       <c r="T92">
-        <v>5.386011617168405</v>
+        <v>5.984457352409339</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05167680156785072</v>
+        <v>0.05110892462754468</v>
       </c>
       <c r="W92">
-        <v>0.2236146101903008</v>
+        <v>0.223748515572825</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2583840078392535</v>
+        <v>0.2555446231377233</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2569186287852293</v>
+        <v>0.2588186287852293</v>
       </c>
       <c r="C93">
-        <v>-46.18423521423897</v>
+        <v>-47.08030632981217</v>
       </c>
       <c r="D93">
-        <v>19.29176478576103</v>
+        <v>19.11969367018784</v>
       </c>
       <c r="E93">
-        <v>46.484</v>
+        <v>47.20800000000001</v>
       </c>
       <c r="F93">
-        <v>65.884</v>
+        <v>66.608</v>
       </c>
       <c r="G93">
         <v>0.408</v>
@@ -9035,37 +9035,37 @@
         <v>3.97</v>
       </c>
       <c r="M93">
-        <v>15.5354472</v>
+        <v>15.7061664</v>
       </c>
       <c r="N93">
-        <v>-11.5654472</v>
+        <v>-11.7361664</v>
       </c>
       <c r="O93">
-        <v>-2.31308944</v>
+        <v>-2.347233280000001</v>
       </c>
       <c r="P93">
-        <v>-9.252357760000001</v>
+        <v>-9.388933120000001</v>
       </c>
       <c r="Q93">
-        <v>-7.572357760000001</v>
+        <v>-7.708933120000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5923053290439841</v>
+        <v>0.6606184951744823</v>
       </c>
       <c r="T93">
-        <v>5.984457352409339</v>
+        <v>6.732514521460508</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05110892462754468</v>
+        <v>0.05055339283811484</v>
       </c>
       <c r="W93">
-        <v>0.223748515572825</v>
+        <v>0.2238795099687725</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2555446231377233</v>
+        <v>0.2527669641905741</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2588186287852293</v>
+        <v>0.2607186287852293</v>
       </c>
       <c r="C94">
-        <v>-47.08030632981217</v>
+        <v>-47.97333503699632</v>
       </c>
       <c r="D94">
-        <v>19.11969367018784</v>
+        <v>18.95066496300368</v>
       </c>
       <c r="E94">
-        <v>47.20800000000001</v>
+        <v>47.93200000000001</v>
       </c>
       <c r="F94">
-        <v>66.608</v>
+        <v>67.33200000000001</v>
       </c>
       <c r="G94">
         <v>0.408</v>
@@ -9117,37 +9117,37 @@
         <v>3.97</v>
       </c>
       <c r="M94">
-        <v>15.7061664</v>
+        <v>15.8768856</v>
       </c>
       <c r="N94">
-        <v>-11.7361664</v>
+        <v>-11.9068856</v>
       </c>
       <c r="O94">
-        <v>-2.347233280000001</v>
+        <v>-2.381377120000001</v>
       </c>
       <c r="P94">
-        <v>-9.388933120000001</v>
+        <v>-9.525508480000003</v>
       </c>
       <c r="Q94">
-        <v>-7.708933120000001</v>
+        <v>-7.845508480000003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6606184951744823</v>
+        <v>0.7484497087708371</v>
       </c>
       <c r="T94">
-        <v>6.732514521460508</v>
+        <v>7.694302310240582</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05055339283811484</v>
+        <v>0.05000980796888779</v>
       </c>
       <c r="W94">
-        <v>0.2238795099687725</v>
+        <v>0.2240076872809363</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2527669641905741</v>
+        <v>0.250049039844439</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2607186287852293</v>
+        <v>0.2626186287852293</v>
       </c>
       <c r="C95">
-        <v>-47.97333503699632</v>
+        <v>-48.86340131843828</v>
       </c>
       <c r="D95">
-        <v>18.95066496300368</v>
+        <v>18.78459868156173</v>
       </c>
       <c r="E95">
-        <v>47.93200000000001</v>
+        <v>48.65600000000001</v>
       </c>
       <c r="F95">
-        <v>67.33200000000001</v>
+        <v>68.05600000000001</v>
       </c>
       <c r="G95">
         <v>0.408</v>
@@ -9199,37 +9199,37 @@
         <v>3.97</v>
       </c>
       <c r="M95">
-        <v>15.8768856</v>
+        <v>16.0476048</v>
       </c>
       <c r="N95">
-        <v>-11.9068856</v>
+        <v>-12.0776048</v>
       </c>
       <c r="O95">
-        <v>-2.381377120000001</v>
+        <v>-2.415520960000001</v>
       </c>
       <c r="P95">
-        <v>-9.525508480000003</v>
+        <v>-9.662083840000003</v>
       </c>
       <c r="Q95">
-        <v>-7.845508480000003</v>
+        <v>-7.982083840000003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7484497087708371</v>
+        <v>0.8655579935659767</v>
       </c>
       <c r="T95">
-        <v>7.694302310240582</v>
+        <v>8.976686028614013</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05000980796888779</v>
+        <v>0.04947778873517622</v>
       </c>
       <c r="W95">
-        <v>0.2240076872809363</v>
+        <v>0.2241331374162454</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.250049039844439</v>
+        <v>0.247388943675881</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2626186287852293</v>
+        <v>0.2645186287852293</v>
       </c>
       <c r="C96">
-        <v>-48.86340131843828</v>
+        <v>-49.75058237756065</v>
       </c>
       <c r="D96">
-        <v>18.78459868156173</v>
+        <v>18.62141762243936</v>
       </c>
       <c r="E96">
-        <v>48.65600000000001</v>
+        <v>49.38000000000002</v>
       </c>
       <c r="F96">
-        <v>68.05600000000001</v>
+        <v>68.78000000000002</v>
       </c>
       <c r="G96">
         <v>0.408</v>
@@ -9281,37 +9281,37 @@
         <v>3.97</v>
       </c>
       <c r="M96">
-        <v>16.0476048</v>
+        <v>16.218324</v>
       </c>
       <c r="N96">
-        <v>-12.0776048</v>
+        <v>-12.248324</v>
       </c>
       <c r="O96">
-        <v>-2.415520960000001</v>
+        <v>-2.449664800000001</v>
       </c>
       <c r="P96">
-        <v>-9.662083840000003</v>
+        <v>-9.798659200000003</v>
       </c>
       <c r="Q96">
-        <v>-7.982083840000003</v>
+        <v>-8.118659200000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8655579935659767</v>
+        <v>1.029509592279173</v>
       </c>
       <c r="T96">
-        <v>8.976686028614013</v>
+        <v>10.77202323433682</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04947778873517622</v>
+        <v>0.04895696990638489</v>
       </c>
       <c r="W96">
-        <v>0.2241331374162454</v>
+        <v>0.2242559464960744</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.247388943675881</v>
+        <v>0.2447848495319244</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2645186287852293</v>
+        <v>0.2664186287852293</v>
       </c>
       <c r="C97">
-        <v>-49.75058237756065</v>
+        <v>-50.63495275823724</v>
       </c>
       <c r="D97">
-        <v>18.62141762243936</v>
+        <v>18.46104724176276</v>
       </c>
       <c r="E97">
-        <v>49.38000000000002</v>
+        <v>50.10400000000001</v>
       </c>
       <c r="F97">
-        <v>68.78000000000002</v>
+        <v>69.504</v>
       </c>
       <c r="G97">
         <v>0.408</v>
@@ -9363,37 +9363,37 @@
         <v>3.97</v>
       </c>
       <c r="M97">
-        <v>16.218324</v>
+        <v>16.3890432</v>
       </c>
       <c r="N97">
-        <v>-12.248324</v>
+        <v>-12.4190432</v>
       </c>
       <c r="O97">
-        <v>-2.449664800000001</v>
+        <v>-2.483808640000001</v>
       </c>
       <c r="P97">
-        <v>-9.798659200000003</v>
+        <v>-9.935234560000003</v>
       </c>
       <c r="Q97">
-        <v>-8.118659200000003</v>
+        <v>-8.255234560000003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.029509592279173</v>
+        <v>1.275436990348966</v>
       </c>
       <c r="T97">
-        <v>10.77202323433682</v>
+        <v>13.46502904292103</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04895696990638489</v>
+        <v>0.04844700146986005</v>
       </c>
       <c r="W97">
-        <v>0.2242559464960744</v>
+        <v>0.224376197053407</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2447848495319244</v>
+        <v>0.2422350073493001</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2664186287852293</v>
+        <v>0.2683186287852293</v>
       </c>
       <c r="C98">
-        <v>-50.63495275823723</v>
+        <v>-51.5165844583373</v>
       </c>
       <c r="D98">
-        <v>18.46104724176277</v>
+        <v>18.30341554166271</v>
       </c>
       <c r="E98">
-        <v>50.10400000000001</v>
+        <v>50.82800000000001</v>
       </c>
       <c r="F98">
-        <v>69.504</v>
+        <v>70.22800000000001</v>
       </c>
       <c r="G98">
         <v>0.408</v>
@@ -9445,37 +9445,37 @@
         <v>3.97</v>
       </c>
       <c r="M98">
-        <v>16.3890432</v>
+        <v>16.5597624</v>
       </c>
       <c r="N98">
-        <v>-12.4190432</v>
+        <v>-12.58976240000001</v>
       </c>
       <c r="O98">
-        <v>-2.483808640000001</v>
+        <v>-2.517952480000001</v>
       </c>
       <c r="P98">
-        <v>-9.935234560000003</v>
+        <v>-10.07180992</v>
       </c>
       <c r="Q98">
-        <v>-8.255234560000003</v>
+        <v>-8.391809920000004</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.275436990348963</v>
+        <v>1.685315987131951</v>
       </c>
       <c r="T98">
-        <v>13.465029042921</v>
+        <v>17.953372057228</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04844700146986005</v>
+        <v>0.04794754784645943</v>
       </c>
       <c r="W98">
-        <v>0.224376197053407</v>
+        <v>0.2244939682178049</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2422350073493001</v>
+        <v>0.239737739232297</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2683186287852293</v>
+        <v>0.2702186287852293</v>
       </c>
       <c r="C99">
-        <v>-51.5165844583373</v>
+        <v>-52.39554703750196</v>
       </c>
       <c r="D99">
-        <v>18.30341554166271</v>
+        <v>18.14845296249803</v>
       </c>
       <c r="E99">
-        <v>50.82800000000001</v>
+        <v>51.552</v>
       </c>
       <c r="F99">
-        <v>70.22800000000001</v>
+        <v>70.952</v>
       </c>
       <c r="G99">
         <v>0.408</v>
@@ -9527,37 +9527,37 @@
         <v>3.97</v>
       </c>
       <c r="M99">
-        <v>16.5597624</v>
+        <v>16.7304816</v>
       </c>
       <c r="N99">
-        <v>-12.58976240000001</v>
+        <v>-12.7604816</v>
       </c>
       <c r="O99">
-        <v>-2.517952480000001</v>
+        <v>-2.55209632</v>
       </c>
       <c r="P99">
-        <v>-10.07180992</v>
+        <v>-10.20838528</v>
       </c>
       <c r="Q99">
-        <v>-8.391809920000004</v>
+        <v>-8.528385280000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.685315987131951</v>
+        <v>2.505073980697926</v>
       </c>
       <c r="T99">
-        <v>17.953372057228</v>
+        <v>26.93005808584199</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04794754784645943</v>
+        <v>0.04745828715414863</v>
       </c>
       <c r="W99">
-        <v>0.2244939682178049</v>
+        <v>0.2246093358890517</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.239737739232297</v>
+        <v>0.2372914357707431</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2702186287852293</v>
+        <v>0.2721186287852293</v>
       </c>
       <c r="C100">
-        <v>-52.39554703750196</v>
+        <v>-53.27190771949191</v>
       </c>
       <c r="D100">
-        <v>18.14845296249803</v>
+        <v>17.99609228050809</v>
       </c>
       <c r="E100">
-        <v>51.552</v>
+        <v>52.276</v>
       </c>
       <c r="F100">
-        <v>70.952</v>
+        <v>71.676</v>
       </c>
       <c r="G100">
         <v>0.408</v>
@@ -9609,37 +9609,37 @@
         <v>3.97</v>
       </c>
       <c r="M100">
-        <v>16.7304816</v>
+        <v>16.9012008</v>
       </c>
       <c r="N100">
-        <v>-12.7604816</v>
+        <v>-12.9312008</v>
       </c>
       <c r="O100">
-        <v>-2.55209632</v>
+        <v>-2.586240160000001</v>
       </c>
       <c r="P100">
-        <v>-10.20838528</v>
+        <v>-10.34496064</v>
       </c>
       <c r="Q100">
-        <v>-8.528385280000002</v>
+        <v>-8.664960640000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.505073980697926</v>
+        <v>4.964347961395852</v>
       </c>
       <c r="T100">
-        <v>26.93005808584199</v>
+        <v>53.86011617168399</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04745828715414863</v>
+        <v>0.04697891051622793</v>
       </c>
       <c r="W100">
-        <v>0.2246093358890517</v>
+        <v>0.2247223729002735</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2372914357707431</v>
+        <v>0.2348945525811396</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2721186287852293</v>
-      </c>
-      <c r="C101">
-        <v>-53.27190771949191</v>
-      </c>
-      <c r="D101">
-        <v>17.99609228050809</v>
-      </c>
-      <c r="E101">
-        <v>52.276</v>
-      </c>
-      <c r="F101">
-        <v>71.676</v>
-      </c>
-      <c r="G101">
-        <v>0.408</v>
-      </c>
-      <c r="H101">
-        <v>53</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.649999999999999</v>
-      </c>
-      <c r="K101">
-        <v>1.68</v>
-      </c>
-      <c r="L101">
-        <v>3.97</v>
-      </c>
-      <c r="M101">
-        <v>16.9012008</v>
-      </c>
-      <c r="N101">
-        <v>-12.9312008</v>
-      </c>
-      <c r="O101">
-        <v>-2.586240160000001</v>
-      </c>
-      <c r="P101">
-        <v>-10.34496064</v>
-      </c>
-      <c r="Q101">
-        <v>-8.664960640000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.964347961395852</v>
-      </c>
-      <c r="T101">
-        <v>53.86011617168399</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04697891051622793</v>
-      </c>
-      <c r="W101">
-        <v>0.2247223729002735</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2348945525811396</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
